--- a/research/traditional_assets/database/data/sweden/sweden_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_oil_gas_distribution.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="om_ccor_b" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06610000000000001</v>
+        <v>-0.077</v>
       </c>
       <c r="G2">
-        <v>0.3217761557177616</v>
+        <v>-0.4514506769825918</v>
       </c>
       <c r="H2">
-        <v>0.2506082725060828</v>
+        <v>-0.5473887814313346</v>
       </c>
       <c r="I2">
-        <v>-0.4914841849148418</v>
+        <v>0.0355899419729207</v>
       </c>
       <c r="J2">
-        <v>-0.4914841849148418</v>
+        <v>0.0355899419729207</v>
       </c>
       <c r="K2">
-        <v>-50.3</v>
+        <v>-29.3</v>
       </c>
       <c r="L2">
-        <v>-0.6119221411192214</v>
+        <v>-0.5667311411992263</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.94</v>
+        <v>4.64</v>
       </c>
       <c r="V2">
-        <v>0.1266881028938907</v>
+        <v>0.1750943396226415</v>
       </c>
       <c r="W2">
-        <v>-0.445527015057573</v>
+        <v>-0.4296187683284458</v>
       </c>
       <c r="X2">
-        <v>0.1701722904403394</v>
+        <v>0.133886752520479</v>
       </c>
       <c r="Y2">
-        <v>-0.6156993054979124</v>
+        <v>-0.5635055208489248</v>
       </c>
       <c r="Z2">
-        <v>0.2935714285714286</v>
+        <v>0.2260010491344641</v>
       </c>
       <c r="AA2">
-        <v>-0.1442857142857143</v>
+        <v>0.008043364224514776</v>
       </c>
       <c r="AB2">
-        <v>0.04264654422414583</v>
+        <v>0.07500347236949796</v>
       </c>
       <c r="AC2">
-        <v>-0.1869322585098601</v>
+        <v>-0.06696010814498318</v>
       </c>
       <c r="AD2">
-        <v>164.5</v>
+        <v>49.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>164.5</v>
+        <v>49.8</v>
       </c>
       <c r="AG2">
-        <v>160.56</v>
+        <v>45.16</v>
       </c>
       <c r="AH2">
-        <v>0.841002044989775</v>
+        <v>0.6526867627785059</v>
       </c>
       <c r="AI2">
-        <v>0.7069187795444779</v>
+        <v>0.6194029850746268</v>
       </c>
       <c r="AJ2">
-        <v>0.8377334863821351</v>
+        <v>0.630198157968183</v>
       </c>
       <c r="AK2">
-        <v>0.7018709564609198</v>
+        <v>0.5960929250263992</v>
       </c>
       <c r="AL2">
-        <v>8.41</v>
+        <v>5.76</v>
       </c>
       <c r="AM2">
-        <v>7.26</v>
+        <v>5.706</v>
       </c>
       <c r="AN2">
-        <v>-6.184210526315789</v>
+        <v>16.49006622516556</v>
       </c>
       <c r="AO2">
-        <v>-4.803804994054697</v>
+        <v>0.3194444444444445</v>
       </c>
       <c r="AP2">
-        <v>-6.03609022556391</v>
+        <v>14.95364238410596</v>
       </c>
       <c r="AQ2">
-        <v>-5.564738292011019</v>
+        <v>0.3224675779880828</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06610000000000001</v>
+        <v>-0.077</v>
       </c>
       <c r="G3">
-        <v>0.3217761557177616</v>
+        <v>-0.4514506769825918</v>
       </c>
       <c r="H3">
-        <v>0.2506082725060828</v>
+        <v>-0.5473887814313346</v>
       </c>
       <c r="I3">
-        <v>-0.4914841849148418</v>
+        <v>0.0355899419729207</v>
       </c>
       <c r="J3">
-        <v>-0.4914841849148418</v>
+        <v>0.0355899419729207</v>
       </c>
       <c r="K3">
-        <v>-50.3</v>
+        <v>-29.3</v>
       </c>
       <c r="L3">
-        <v>-0.6119221411192214</v>
+        <v>-0.5667311411992263</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8774 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.94</v>
+        <v>4.64</v>
       </c>
       <c r="V3">
-        <v>0.1266881028938907</v>
+        <v>0.1750943396226415</v>
       </c>
       <c r="W3">
-        <v>-0.445527015057573</v>
+        <v>-0.4296187683284458</v>
       </c>
       <c r="X3">
-        <v>0.1701722904403394</v>
+        <v>0.133886752520479</v>
       </c>
       <c r="Y3">
-        <v>-0.6156993054979124</v>
+        <v>-0.5635055208489248</v>
       </c>
       <c r="Z3">
-        <v>0.2935714285714286</v>
+        <v>0.2260010491344641</v>
       </c>
       <c r="AA3">
-        <v>-0.1442857142857143</v>
+        <v>0.008043364224514776</v>
       </c>
       <c r="AB3">
-        <v>0.04264654422414583</v>
+        <v>0.07500347236949796</v>
       </c>
       <c r="AC3">
-        <v>-0.1869322585098601</v>
+        <v>-0.06696010814498318</v>
       </c>
       <c r="AD3">
-        <v>164.5</v>
+        <v>49.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>164.5</v>
+        <v>49.8</v>
       </c>
       <c r="AG3">
-        <v>160.56</v>
+        <v>45.16</v>
       </c>
       <c r="AH3">
-        <v>0.841002044989775</v>
+        <v>0.6526867627785059</v>
       </c>
       <c r="AI3">
-        <v>0.7069187795444779</v>
+        <v>0.6194029850746268</v>
       </c>
       <c r="AJ3">
-        <v>0.8377334863821351</v>
+        <v>0.630198157968183</v>
       </c>
       <c r="AK3">
-        <v>0.7018709564609198</v>
+        <v>0.5960929250263992</v>
       </c>
       <c r="AL3">
-        <v>8.41</v>
+        <v>5.76</v>
       </c>
       <c r="AM3">
-        <v>7.26</v>
+        <v>5.706</v>
       </c>
       <c r="AN3">
-        <v>-6.184210526315789</v>
+        <v>16.49006622516556</v>
       </c>
       <c r="AO3">
-        <v>-4.803804994054697</v>
+        <v>0.3194444444444445</v>
       </c>
       <c r="AP3">
-        <v>-6.03609022556391</v>
+        <v>14.95364238410596</v>
       </c>
       <c r="AQ3">
-        <v>-5.564738292011019</v>
+        <v>0.3224675779880828</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Concordia Maritime AB (publ) (OM:CCOR B)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OM:CCOR B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas Distribution</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.652686762778506</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>26.5</v>
+      </c>
+      <c r="H2">
+        <v>51.0088326956581</v>
+      </c>
+      <c r="I2">
+        <v>71.66</v>
+      </c>
+      <c r="J2">
+        <v>47.1318326956581</v>
+      </c>
+      <c r="K2">
+        <v>49.8</v>
+      </c>
+      <c r="L2">
+        <v>0.763</v>
+      </c>
+      <c r="M2">
+        <v>0.075003472369498</v>
+      </c>
+      <c r="N2">
+        <v>0.122103554517217</v>
+      </c>
+      <c r="O2">
+        <v>0.04367</v>
+      </c>
+      <c r="P2">
+        <v>3.95921939711664</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.133886752520479</v>
+      </c>
+      <c r="T2">
+        <v>0.08334480863237451</v>
+      </c>
+      <c r="U2">
+        <v>1.60775936589569</v>
+      </c>
+      <c r="V2">
+        <v>0.753178874894343</v>
+      </c>
+      <c r="W2">
+        <v>-75.62934813868381</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>26.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.055</v>
+      </c>
+      <c r="AD2">
+        <v>0.206</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>3.02</v>
+      </c>
+      <c r="AH2">
+        <v>16.8</v>
+      </c>
+      <c r="AI2">
+        <v>-0.7290000000000003</v>
+      </c>
+      <c r="AJ2">
+        <v>49.8</v>
+      </c>
+      <c r="AK2">
+        <v>49.8</v>
+      </c>
+      <c r="AL2">
+        <v>5.76</v>
+      </c>
+      <c r="AM2">
+        <v>49.8</v>
+      </c>
+      <c r="AN2">
+        <v>4.64</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-49.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.64</v>
+      </c>
+      <c r="H2">
+        <v>26.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.02</v>
+      </c>
+      <c r="K2">
+        <v>16.8</v>
+      </c>
+      <c r="L2">
+        <v>-13.78</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-13.78</v>
+      </c>
+      <c r="O2">
+        <v>-2.83868</v>
+      </c>
+      <c r="P2">
+        <v>-10.94132</v>
+      </c>
+      <c r="Q2">
+        <v>5.85868</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1221035545172172</v>
+      </c>
+      <c r="C3">
+        <v>51.00883269565809</v>
+      </c>
+      <c r="D3">
+        <v>47.13183269565808</v>
+      </c>
+      <c r="E3">
+        <v>-49.037</v>
+      </c>
+      <c r="F3">
+        <v>0.763</v>
+      </c>
+      <c r="G3">
+        <v>4.64</v>
+      </c>
+      <c r="H3">
+        <v>26.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.02</v>
+      </c>
+      <c r="K3">
+        <v>16.8</v>
+      </c>
+      <c r="L3">
+        <v>-13.78</v>
+      </c>
+      <c r="M3">
+        <v>0.1822044</v>
+      </c>
+      <c r="N3">
+        <v>-13.9622044</v>
+      </c>
+      <c r="O3">
+        <v>-2.8762141064</v>
+      </c>
+      <c r="P3">
+        <v>-11.0859902936</v>
+      </c>
+      <c r="Q3">
+        <v>5.714009706399999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08334480863237451</v>
+      </c>
+      <c r="T3">
+        <v>0.7531788748943432</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-15.57964571656886</v>
+      </c>
+      <c r="W3">
+        <v>3.959219397116645</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-75.62934813868381</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1241035545172172</v>
+      </c>
+      <c r="C4">
+        <v>49.57061442700369</v>
+      </c>
+      <c r="D4">
+        <v>46.45661442700369</v>
+      </c>
+      <c r="E4">
+        <v>-48.27399999999999</v>
+      </c>
+      <c r="F4">
+        <v>1.526</v>
+      </c>
+      <c r="G4">
+        <v>4.64</v>
+      </c>
+      <c r="H4">
+        <v>26.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.02</v>
+      </c>
+      <c r="K4">
+        <v>16.8</v>
+      </c>
+      <c r="L4">
+        <v>-13.78</v>
+      </c>
+      <c r="M4">
+        <v>0.3644088</v>
+      </c>
+      <c r="N4">
+        <v>-14.1444088</v>
+      </c>
+      <c r="O4">
+        <v>-2.913748212799999</v>
+      </c>
+      <c r="P4">
+        <v>-11.2306605872</v>
+      </c>
+      <c r="Q4">
+        <v>5.5693394128</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08379934749597016</v>
+      </c>
+      <c r="T4">
+        <v>0.7608643736177549</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-7.789822858284431</v>
+      </c>
+      <c r="W4">
+        <v>2.099009698558322</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-37.8146740693419</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1261035545172172</v>
+      </c>
+      <c r="C5">
+        <v>48.15146948335588</v>
+      </c>
+      <c r="D5">
+        <v>45.80046948335588</v>
+      </c>
+      <c r="E5">
+        <v>-47.511</v>
+      </c>
+      <c r="F5">
+        <v>2.289</v>
+      </c>
+      <c r="G5">
+        <v>4.64</v>
+      </c>
+      <c r="H5">
+        <v>26.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.02</v>
+      </c>
+      <c r="K5">
+        <v>16.8</v>
+      </c>
+      <c r="L5">
+        <v>-13.78</v>
+      </c>
+      <c r="M5">
+        <v>0.5466131999999999</v>
+      </c>
+      <c r="N5">
+        <v>-14.3266132</v>
+      </c>
+      <c r="O5">
+        <v>-2.9512823192</v>
+      </c>
+      <c r="P5">
+        <v>-11.3753308808</v>
+      </c>
+      <c r="Q5">
+        <v>5.424669119200001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0842632582948977</v>
+      </c>
+      <c r="T5">
+        <v>0.7687083362323709</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-5.193215238856288</v>
+      </c>
+      <c r="W5">
+        <v>1.478939799038882</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-25.20978271289461</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1281035545172172</v>
+      </c>
+      <c r="C6">
+        <v>46.75060095538935</v>
+      </c>
+      <c r="D6">
+        <v>45.16260095538935</v>
+      </c>
+      <c r="E6">
+        <v>-46.748</v>
+      </c>
+      <c r="F6">
+        <v>3.052</v>
+      </c>
+      <c r="G6">
+        <v>4.64</v>
+      </c>
+      <c r="H6">
+        <v>26.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.02</v>
+      </c>
+      <c r="K6">
+        <v>16.8</v>
+      </c>
+      <c r="L6">
+        <v>-13.78</v>
+      </c>
+      <c r="M6">
+        <v>0.7288176000000001</v>
+      </c>
+      <c r="N6">
+        <v>-14.5088176</v>
+      </c>
+      <c r="O6">
+        <v>-2.9888164256</v>
+      </c>
+      <c r="P6">
+        <v>-11.5200011744</v>
+      </c>
+      <c r="Q6">
+        <v>5.2799988256</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08473683390213621</v>
+      </c>
+      <c r="T6">
+        <v>0.7767157147347914</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-3.894911429142216</v>
+      </c>
+      <c r="W6">
+        <v>1.168904849279161</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-18.90733703467095</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1301035545172172</v>
+      </c>
+      <c r="C7">
+        <v>45.36725571858241</v>
+      </c>
+      <c r="D7">
+        <v>44.5422557185824</v>
+      </c>
+      <c r="E7">
+        <v>-45.985</v>
+      </c>
+      <c r="F7">
+        <v>3.815</v>
+      </c>
+      <c r="G7">
+        <v>4.64</v>
+      </c>
+      <c r="H7">
+        <v>26.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.02</v>
+      </c>
+      <c r="K7">
+        <v>16.8</v>
+      </c>
+      <c r="L7">
+        <v>-13.78</v>
+      </c>
+      <c r="M7">
+        <v>0.911022</v>
+      </c>
+      <c r="N7">
+        <v>-14.691022</v>
+      </c>
+      <c r="O7">
+        <v>-3.026350531999999</v>
+      </c>
+      <c r="P7">
+        <v>-11.664671468</v>
+      </c>
+      <c r="Q7">
+        <v>5.135328531999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08522037952215869</v>
+      </c>
+      <c r="T7">
+        <v>0.7848916696267366</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-3.115929143313773</v>
+      </c>
+      <c r="W7">
+        <v>0.982883879423329</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-15.12586962773676</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1321035545172172</v>
+      </c>
+      <c r="C8">
+        <v>44.00072146686207</v>
+      </c>
+      <c r="D8">
+        <v>43.93872146686208</v>
+      </c>
+      <c r="E8">
+        <v>-45.22199999999999</v>
+      </c>
+      <c r="F8">
+        <v>4.577999999999999</v>
+      </c>
+      <c r="G8">
+        <v>4.64</v>
+      </c>
+      <c r="H8">
+        <v>26.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.02</v>
+      </c>
+      <c r="K8">
+        <v>16.8</v>
+      </c>
+      <c r="L8">
+        <v>-13.78</v>
+      </c>
+      <c r="M8">
+        <v>1.0932264</v>
+      </c>
+      <c r="N8">
+        <v>-14.8732264</v>
+      </c>
+      <c r="O8">
+        <v>-3.063884638399999</v>
+      </c>
+      <c r="P8">
+        <v>-11.8093417616</v>
+      </c>
+      <c r="Q8">
+        <v>4.9906582384</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08571421334686252</v>
+      </c>
+      <c r="T8">
+        <v>0.7932415810057445</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-2.596607619428144</v>
+      </c>
+      <c r="W8">
+        <v>0.8588698995194408</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-12.6048913564473</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1341035545172172</v>
+      </c>
+      <c r="C9">
+        <v>42.6503239841844</v>
+      </c>
+      <c r="D9">
+        <v>43.3513239841844</v>
+      </c>
+      <c r="E9">
+        <v>-44.459</v>
+      </c>
+      <c r="F9">
+        <v>5.341</v>
+      </c>
+      <c r="G9">
+        <v>4.64</v>
+      </c>
+      <c r="H9">
+        <v>26.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.02</v>
+      </c>
+      <c r="K9">
+        <v>16.8</v>
+      </c>
+      <c r="L9">
+        <v>-13.78</v>
+      </c>
+      <c r="M9">
+        <v>1.2754308</v>
+      </c>
+      <c r="N9">
+        <v>-15.0554308</v>
+      </c>
+      <c r="O9">
+        <v>-3.1014187448</v>
+      </c>
+      <c r="P9">
+        <v>-11.9540120552</v>
+      </c>
+      <c r="Q9">
+        <v>4.845987944799999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08621866725381802</v>
+      </c>
+      <c r="T9">
+        <v>0.8017710603713977</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-2.225663673795552</v>
+      </c>
+      <c r="W9">
+        <v>0.7702884853023778</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-10.80419259124054</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1361035545172172</v>
+      </c>
+      <c r="C10">
+        <v>41.31542463207802</v>
+      </c>
+      <c r="D10">
+        <v>42.77942463207802</v>
+      </c>
+      <c r="E10">
+        <v>-43.696</v>
+      </c>
+      <c r="F10">
+        <v>6.104</v>
+      </c>
+      <c r="G10">
+        <v>4.64</v>
+      </c>
+      <c r="H10">
+        <v>26.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.02</v>
+      </c>
+      <c r="K10">
+        <v>16.8</v>
+      </c>
+      <c r="L10">
+        <v>-13.78</v>
+      </c>
+      <c r="M10">
+        <v>1.4576352</v>
+      </c>
+      <c r="N10">
+        <v>-15.2376352</v>
+      </c>
+      <c r="O10">
+        <v>-3.1389528512</v>
+      </c>
+      <c r="P10">
+        <v>-12.0986823488</v>
+      </c>
+      <c r="Q10">
+        <v>4.701317651199998</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08673408755005517</v>
+      </c>
+      <c r="T10">
+        <v>0.8104859632015214</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-1.947455714571108</v>
+      </c>
+      <c r="W10">
+        <v>0.7038524246395805</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-9.453668517335476</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1381035545172172</v>
+      </c>
+      <c r="C11">
+        <v>39.99541803346723</v>
+      </c>
+      <c r="D11">
+        <v>42.22241803346723</v>
+      </c>
+      <c r="E11">
+        <v>-42.933</v>
+      </c>
+      <c r="F11">
+        <v>6.866999999999999</v>
+      </c>
+      <c r="G11">
+        <v>4.64</v>
+      </c>
+      <c r="H11">
+        <v>26.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.02</v>
+      </c>
+      <c r="K11">
+        <v>16.8</v>
+      </c>
+      <c r="L11">
+        <v>-13.78</v>
+      </c>
+      <c r="M11">
+        <v>1.6398396</v>
+      </c>
+      <c r="N11">
+        <v>-15.4198396</v>
+      </c>
+      <c r="O11">
+        <v>-3.1764869576</v>
+      </c>
+      <c r="P11">
+        <v>-12.2433526424</v>
+      </c>
+      <c r="Q11">
+        <v>4.556647357599999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08726083576489094</v>
+      </c>
+      <c r="T11">
+        <v>0.8193924023575822</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-1.731071746285429</v>
+      </c>
+      <c r="W11">
+        <v>0.6521799330129605</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-8.403260904298202</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1401035545172172</v>
+      </c>
+      <c r="C12">
+        <v>38.68972993511522</v>
+      </c>
+      <c r="D12">
+        <v>41.67972993511522</v>
+      </c>
+      <c r="E12">
+        <v>-42.16999999999999</v>
+      </c>
+      <c r="F12">
+        <v>7.63</v>
+      </c>
+      <c r="G12">
+        <v>4.64</v>
+      </c>
+      <c r="H12">
+        <v>26.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.02</v>
+      </c>
+      <c r="K12">
+        <v>16.8</v>
+      </c>
+      <c r="L12">
+        <v>-13.78</v>
+      </c>
+      <c r="M12">
+        <v>1.822044</v>
+      </c>
+      <c r="N12">
+        <v>-15.602044</v>
+      </c>
+      <c r="O12">
+        <v>-3.214021064</v>
+      </c>
+      <c r="P12">
+        <v>-12.388022936</v>
+      </c>
+      <c r="Q12">
+        <v>4.411977063999998</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08779928949561196</v>
+      </c>
+      <c r="T12">
+        <v>0.8284967623837776</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-1.557964571656886</v>
+      </c>
+      <c r="W12">
+        <v>0.6108419397116645</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-7.562934813868381</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1421035545172172</v>
+      </c>
+      <c r="C13">
+        <v>37.39781523282051</v>
+      </c>
+      <c r="D13">
+        <v>41.15081523282051</v>
+      </c>
+      <c r="E13">
+        <v>-41.407</v>
+      </c>
+      <c r="F13">
+        <v>8.392999999999999</v>
+      </c>
+      <c r="G13">
+        <v>4.64</v>
+      </c>
+      <c r="H13">
+        <v>26.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.02</v>
+      </c>
+      <c r="K13">
+        <v>16.8</v>
+      </c>
+      <c r="L13">
+        <v>-13.78</v>
+      </c>
+      <c r="M13">
+        <v>2.0042484</v>
+      </c>
+      <c r="N13">
+        <v>-15.7842484</v>
+      </c>
+      <c r="O13">
+        <v>-3.2515551704</v>
+      </c>
+      <c r="P13">
+        <v>-12.5326932296</v>
+      </c>
+      <c r="Q13">
+        <v>4.267306770399999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.0883498433101694</v>
+      </c>
+      <c r="T13">
+        <v>0.8378057147701122</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-1.416331428778988</v>
+      </c>
+      <c r="W13">
+        <v>0.5770199451924224</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-6.875395285334893</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1441035545172172</v>
+      </c>
+      <c r="C14">
+        <v>36.11915614509039</v>
+      </c>
+      <c r="D14">
+        <v>40.63515614509039</v>
+      </c>
+      <c r="E14">
+        <v>-40.644</v>
+      </c>
+      <c r="F14">
+        <v>9.155999999999999</v>
+      </c>
+      <c r="G14">
+        <v>4.64</v>
+      </c>
+      <c r="H14">
+        <v>26.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.02</v>
+      </c>
+      <c r="K14">
+        <v>16.8</v>
+      </c>
+      <c r="L14">
+        <v>-13.78</v>
+      </c>
+      <c r="M14">
+        <v>2.1864528</v>
+      </c>
+      <c r="N14">
+        <v>-15.9664528</v>
+      </c>
+      <c r="O14">
+        <v>-3.2890892768</v>
+      </c>
+      <c r="P14">
+        <v>-12.6773635232</v>
+      </c>
+      <c r="Q14">
+        <v>4.1226364768</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08891290971142132</v>
+      </c>
+      <c r="T14">
+        <v>0.8473262342561362</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-1.298303809714072</v>
+      </c>
+      <c r="W14">
+        <v>0.5488349497597205</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-6.302445678223652</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1461035545172172</v>
+      </c>
+      <c r="C15">
+        <v>34.85326052242877</v>
+      </c>
+      <c r="D15">
+        <v>40.13226052242877</v>
+      </c>
+      <c r="E15">
+        <v>-39.881</v>
+      </c>
+      <c r="F15">
+        <v>9.919</v>
+      </c>
+      <c r="G15">
+        <v>4.64</v>
+      </c>
+      <c r="H15">
+        <v>26.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.02</v>
+      </c>
+      <c r="K15">
+        <v>16.8</v>
+      </c>
+      <c r="L15">
+        <v>-13.78</v>
+      </c>
+      <c r="M15">
+        <v>2.3686572</v>
+      </c>
+      <c r="N15">
+        <v>-16.1486572</v>
+      </c>
+      <c r="O15">
+        <v>-3.3266233832</v>
+      </c>
+      <c r="P15">
+        <v>-12.8220338168</v>
+      </c>
+      <c r="Q15">
+        <v>3.977966183199998</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08948892016787444</v>
+      </c>
+      <c r="T15">
+        <v>0.8570656162590803</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-1.198434285889912</v>
+      </c>
+      <c r="W15">
+        <v>0.5249861074705111</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-5.817642164514139</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1481035545172172</v>
+      </c>
+      <c r="C16">
+        <v>33.59966028063348</v>
+      </c>
+      <c r="D16">
+        <v>39.64166028063348</v>
+      </c>
+      <c r="E16">
+        <v>-39.11799999999999</v>
+      </c>
+      <c r="F16">
+        <v>10.682</v>
+      </c>
+      <c r="G16">
+        <v>4.64</v>
+      </c>
+      <c r="H16">
+        <v>26.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.02</v>
+      </c>
+      <c r="K16">
+        <v>16.8</v>
+      </c>
+      <c r="L16">
+        <v>-13.78</v>
+      </c>
+      <c r="M16">
+        <v>2.5508616</v>
+      </c>
+      <c r="N16">
+        <v>-16.3308616</v>
+      </c>
+      <c r="O16">
+        <v>-3.3641574896</v>
+      </c>
+      <c r="P16">
+        <v>-12.9667041104</v>
+      </c>
+      <c r="Q16">
+        <v>3.833295889599999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.0900783262163381</v>
+      </c>
+      <c r="T16">
+        <v>0.8670314955179067</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-1.112831836897776</v>
+      </c>
+      <c r="W16">
+        <v>0.5045442426511889</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-5.402096295620272</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1501035545172172</v>
+      </c>
+      <c r="C17">
+        <v>32.3579099476197</v>
+      </c>
+      <c r="D17">
+        <v>39.1629099476197</v>
+      </c>
+      <c r="E17">
+        <v>-38.355</v>
+      </c>
+      <c r="F17">
+        <v>11.445</v>
+      </c>
+      <c r="G17">
+        <v>4.64</v>
+      </c>
+      <c r="H17">
+        <v>26.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.02</v>
+      </c>
+      <c r="K17">
+        <v>16.8</v>
+      </c>
+      <c r="L17">
+        <v>-13.78</v>
+      </c>
+      <c r="M17">
+        <v>2.733066</v>
+      </c>
+      <c r="N17">
+        <v>-16.513066</v>
+      </c>
+      <c r="O17">
+        <v>-3.401691596</v>
+      </c>
+      <c r="P17">
+        <v>-13.111374404</v>
+      </c>
+      <c r="Q17">
+        <v>3.688625595999998</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09068160064241265</v>
+      </c>
+      <c r="T17">
+        <v>0.8772318660534115</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-1.038643047771258</v>
+      </c>
+      <c r="W17">
+        <v>0.4868279598077763</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-5.041956542578921</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1521035545172172</v>
+      </c>
+      <c r="C18">
+        <v>31.12758531428621</v>
+      </c>
+      <c r="D18">
+        <v>38.69558531428621</v>
+      </c>
+      <c r="E18">
+        <v>-37.592</v>
+      </c>
+      <c r="F18">
+        <v>12.208</v>
+      </c>
+      <c r="G18">
+        <v>4.64</v>
+      </c>
+      <c r="H18">
+        <v>26.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.02</v>
+      </c>
+      <c r="K18">
+        <v>16.8</v>
+      </c>
+      <c r="L18">
+        <v>-13.78</v>
+      </c>
+      <c r="M18">
+        <v>2.9152704</v>
+      </c>
+      <c r="N18">
+        <v>-16.6952704</v>
+      </c>
+      <c r="O18">
+        <v>-3.4392257024</v>
+      </c>
+      <c r="P18">
+        <v>-13.2560446976</v>
+      </c>
+      <c r="Q18">
+        <v>3.543955302399999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09129923874529852</v>
+      </c>
+      <c r="T18">
+        <v>0.8876751025540474</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.9737278572855539</v>
+      </c>
+      <c r="W18">
+        <v>0.4713262123197903</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-4.726834258667738</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1541035545172172</v>
+      </c>
+      <c r="C19">
+        <v>29.9082821808368</v>
+      </c>
+      <c r="D19">
+        <v>38.2392821808368</v>
+      </c>
+      <c r="E19">
+        <v>-36.82899999999999</v>
+      </c>
+      <c r="F19">
+        <v>12.971</v>
+      </c>
+      <c r="G19">
+        <v>4.64</v>
+      </c>
+      <c r="H19">
+        <v>26.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.02</v>
+      </c>
+      <c r="K19">
+        <v>16.8</v>
+      </c>
+      <c r="L19">
+        <v>-13.78</v>
+      </c>
+      <c r="M19">
+        <v>3.0974748</v>
+      </c>
+      <c r="N19">
+        <v>-16.8774748</v>
+      </c>
+      <c r="O19">
+        <v>-3.4767598088</v>
+      </c>
+      <c r="P19">
+        <v>-13.4007149912</v>
+      </c>
+      <c r="Q19">
+        <v>3.3992850088</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09193175969403705</v>
+      </c>
+      <c r="T19">
+        <v>0.8983699833077106</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.9164497480334625</v>
+      </c>
+      <c r="W19">
+        <v>0.4576481998303908</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-4.44878518462846</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1561035545172172</v>
+      </c>
+      <c r="C20">
+        <v>28.69961519076903</v>
+      </c>
+      <c r="D20">
+        <v>37.79361519076902</v>
+      </c>
+      <c r="E20">
+        <v>-36.066</v>
+      </c>
+      <c r="F20">
+        <v>13.734</v>
+      </c>
+      <c r="G20">
+        <v>4.64</v>
+      </c>
+      <c r="H20">
+        <v>26.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.02</v>
+      </c>
+      <c r="K20">
+        <v>16.8</v>
+      </c>
+      <c r="L20">
+        <v>-13.78</v>
+      </c>
+      <c r="M20">
+        <v>3.2796792</v>
+      </c>
+      <c r="N20">
+        <v>-17.0596792</v>
+      </c>
+      <c r="O20">
+        <v>-3.5142939152</v>
+      </c>
+      <c r="P20">
+        <v>-13.5453852848</v>
+      </c>
+      <c r="Q20">
+        <v>3.254614715199999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09257970798298873</v>
+      </c>
+      <c r="T20">
+        <v>0.9093257148114631</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.8655358731427146</v>
+      </c>
+      <c r="W20">
+        <v>0.4454899665064803</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-4.201630452149101</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1581035545172172</v>
+      </c>
+      <c r="C21">
+        <v>27.50121674546053</v>
+      </c>
+      <c r="D21">
+        <v>37.35821674546053</v>
+      </c>
+      <c r="E21">
+        <v>-35.303</v>
+      </c>
+      <c r="F21">
+        <v>14.497</v>
+      </c>
+      <c r="G21">
+        <v>4.64</v>
+      </c>
+      <c r="H21">
+        <v>26.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.02</v>
+      </c>
+      <c r="K21">
+        <v>16.8</v>
+      </c>
+      <c r="L21">
+        <v>-13.78</v>
+      </c>
+      <c r="M21">
+        <v>3.4618836</v>
+      </c>
+      <c r="N21">
+        <v>-17.2418836</v>
+      </c>
+      <c r="O21">
+        <v>-3.5518280216</v>
+      </c>
+      <c r="P21">
+        <v>-13.6900555784</v>
+      </c>
+      <c r="Q21">
+        <v>3.109944421599998</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09324365499512439</v>
+      </c>
+      <c r="T21">
+        <v>0.9205519582041973</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.8199813535036243</v>
+      </c>
+      <c r="W21">
+        <v>0.4346115472166656</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-3.980492007299148</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1601035545172172</v>
+      </c>
+      <c r="C22">
+        <v>26.31273599292758</v>
+      </c>
+      <c r="D22">
+        <v>36.93273599292758</v>
+      </c>
+      <c r="E22">
+        <v>-34.54</v>
+      </c>
+      <c r="F22">
+        <v>15.26</v>
+      </c>
+      <c r="G22">
+        <v>4.64</v>
+      </c>
+      <c r="H22">
+        <v>26.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.02</v>
+      </c>
+      <c r="K22">
+        <v>16.8</v>
+      </c>
+      <c r="L22">
+        <v>-13.78</v>
+      </c>
+      <c r="M22">
+        <v>3.644088</v>
+      </c>
+      <c r="N22">
+        <v>-17.424088</v>
+      </c>
+      <c r="O22">
+        <v>-3.589362127999999</v>
+      </c>
+      <c r="P22">
+        <v>-13.834725872</v>
+      </c>
+      <c r="Q22">
+        <v>2.965274127999999</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09392420068256344</v>
+      </c>
+      <c r="T22">
+        <v>0.9320588576817497</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.7789822858284432</v>
+      </c>
+      <c r="W22">
+        <v>0.4248209698558322</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-3.78146740693419</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1621035545172172</v>
+      </c>
+      <c r="C23">
+        <v>25.13383788490873</v>
+      </c>
+      <c r="D23">
+        <v>36.51683788490873</v>
+      </c>
+      <c r="E23">
+        <v>-33.777</v>
+      </c>
+      <c r="F23">
+        <v>16.023</v>
+      </c>
+      <c r="G23">
+        <v>4.64</v>
+      </c>
+      <c r="H23">
+        <v>26.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.02</v>
+      </c>
+      <c r="K23">
+        <v>16.8</v>
+      </c>
+      <c r="L23">
+        <v>-13.78</v>
+      </c>
+      <c r="M23">
+        <v>3.8262924</v>
+      </c>
+      <c r="N23">
+        <v>-17.6062924</v>
+      </c>
+      <c r="O23">
+        <v>-3.626896234399999</v>
+      </c>
+      <c r="P23">
+        <v>-13.9793961656</v>
+      </c>
+      <c r="Q23">
+        <v>2.8206038344</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09462197537474779</v>
+      </c>
+      <c r="T23">
+        <v>0.9438570710701263</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.741887891265184</v>
+      </c>
+      <c r="W23">
+        <v>0.415962828434126</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-3.601397530413514</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1641035545172172</v>
+      </c>
+      <c r="C24">
+        <v>23.9642022969481</v>
+      </c>
+      <c r="D24">
+        <v>36.1102022969481</v>
+      </c>
+      <c r="E24">
+        <v>-33.014</v>
+      </c>
+      <c r="F24">
+        <v>16.786</v>
+      </c>
+      <c r="G24">
+        <v>4.64</v>
+      </c>
+      <c r="H24">
+        <v>26.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.02</v>
+      </c>
+      <c r="K24">
+        <v>16.8</v>
+      </c>
+      <c r="L24">
+        <v>-13.78</v>
+      </c>
+      <c r="M24">
+        <v>4.0084968</v>
+      </c>
+      <c r="N24">
+        <v>-17.7884968</v>
+      </c>
+      <c r="O24">
+        <v>-3.6644303408</v>
+      </c>
+      <c r="P24">
+        <v>-14.1240664592</v>
+      </c>
+      <c r="Q24">
+        <v>2.675933540799999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09533764172570611</v>
+      </c>
+      <c r="T24">
+        <v>0.9559578027505127</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.7081657143894938</v>
+      </c>
+      <c r="W24">
+        <v>0.4079099725962112</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-3.437697642667446</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1661035545172172</v>
+      </c>
+      <c r="C25">
+        <v>22.80352320662129</v>
+      </c>
+      <c r="D25">
+        <v>35.71252320662129</v>
+      </c>
+      <c r="E25">
+        <v>-32.251</v>
+      </c>
+      <c r="F25">
+        <v>17.549</v>
+      </c>
+      <c r="G25">
+        <v>4.64</v>
+      </c>
+      <c r="H25">
+        <v>26.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.02</v>
+      </c>
+      <c r="K25">
+        <v>16.8</v>
+      </c>
+      <c r="L25">
+        <v>-13.78</v>
+      </c>
+      <c r="M25">
+        <v>4.1907012</v>
+      </c>
+      <c r="N25">
+        <v>-17.9707012</v>
+      </c>
+      <c r="O25">
+        <v>-3.7019644472</v>
+      </c>
+      <c r="P25">
+        <v>-14.2687367528</v>
+      </c>
+      <c r="Q25">
+        <v>2.5312632472</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09607189681305295</v>
+      </c>
+      <c r="T25">
+        <v>0.9683728391498699</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.6773759007203853</v>
+      </c>
+      <c r="W25">
+        <v>0.4005573650920281</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-3.288232527768861</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1681035545172172</v>
+      </c>
+      <c r="C26">
+        <v>21.65150792547069</v>
+      </c>
+      <c r="D26">
+        <v>35.32350792547069</v>
+      </c>
+      <c r="E26">
+        <v>-31.488</v>
+      </c>
+      <c r="F26">
+        <v>18.312</v>
+      </c>
+      <c r="G26">
+        <v>4.64</v>
+      </c>
+      <c r="H26">
+        <v>26.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.02</v>
+      </c>
+      <c r="K26">
+        <v>16.8</v>
+      </c>
+      <c r="L26">
+        <v>-13.78</v>
+      </c>
+      <c r="M26">
+        <v>4.372905599999999</v>
+      </c>
+      <c r="N26">
+        <v>-18.1529056</v>
+      </c>
+      <c r="O26">
+        <v>-3.739498553599999</v>
+      </c>
+      <c r="P26">
+        <v>-14.4134070464</v>
+      </c>
+      <c r="Q26">
+        <v>2.386592953599999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09682547440269837</v>
+      </c>
+      <c r="T26">
+        <v>0.9811145870334208</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.649151904857036</v>
+      </c>
+      <c r="W26">
+        <v>0.3938174748798602</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-3.151222839111826</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1701035545172172</v>
+      </c>
+      <c r="C27">
+        <v>20.50787638059878</v>
+      </c>
+      <c r="D27">
+        <v>34.94287638059878</v>
+      </c>
+      <c r="E27">
+        <v>-30.725</v>
+      </c>
+      <c r="F27">
+        <v>19.075</v>
+      </c>
+      <c r="G27">
+        <v>4.64</v>
+      </c>
+      <c r="H27">
+        <v>26.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.02</v>
+      </c>
+      <c r="K27">
+        <v>16.8</v>
+      </c>
+      <c r="L27">
+        <v>-13.78</v>
+      </c>
+      <c r="M27">
+        <v>4.55511</v>
+      </c>
+      <c r="N27">
+        <v>-18.33511</v>
+      </c>
+      <c r="O27">
+        <v>-3.777032659999999</v>
+      </c>
+      <c r="P27">
+        <v>-14.55807734</v>
+      </c>
+      <c r="Q27">
+        <v>2.24192266</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09759914739473435</v>
+      </c>
+      <c r="T27">
+        <v>0.9941961148605332</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.6231858286627545</v>
+      </c>
+      <c r="W27">
+        <v>0.3876167758846658</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-3.025173925547352</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1721035545172172</v>
+      </c>
+      <c r="C28">
+        <v>19.37236044221402</v>
+      </c>
+      <c r="D28">
+        <v>34.57036044221402</v>
+      </c>
+      <c r="E28">
+        <v>-29.962</v>
+      </c>
+      <c r="F28">
+        <v>19.838</v>
+      </c>
+      <c r="G28">
+        <v>4.64</v>
+      </c>
+      <c r="H28">
+        <v>26.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.02</v>
+      </c>
+      <c r="K28">
+        <v>16.8</v>
+      </c>
+      <c r="L28">
+        <v>-13.78</v>
+      </c>
+      <c r="M28">
+        <v>4.737314400000001</v>
+      </c>
+      <c r="N28">
+        <v>-18.5173144</v>
+      </c>
+      <c r="O28">
+        <v>-3.8145667664</v>
+      </c>
+      <c r="P28">
+        <v>-14.7027476336</v>
+      </c>
+      <c r="Q28">
+        <v>2.097252366399998</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09839373046763616</v>
+      </c>
+      <c r="T28">
+        <v>1.007631197493783</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.5992171429449562</v>
+      </c>
+      <c r="W28">
+        <v>0.3818930537352556</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-2.90882108225707</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1741035545172172</v>
+      </c>
+      <c r="C29">
+        <v>18.24470329373578</v>
+      </c>
+      <c r="D29">
+        <v>34.20570329373578</v>
+      </c>
+      <c r="E29">
+        <v>-29.199</v>
+      </c>
+      <c r="F29">
+        <v>20.601</v>
+      </c>
+      <c r="G29">
+        <v>4.64</v>
+      </c>
+      <c r="H29">
+        <v>26.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.02</v>
+      </c>
+      <c r="K29">
+        <v>16.8</v>
+      </c>
+      <c r="L29">
+        <v>-13.78</v>
+      </c>
+      <c r="M29">
+        <v>4.9195188</v>
+      </c>
+      <c r="N29">
+        <v>-18.6995188</v>
+      </c>
+      <c r="O29">
+        <v>-3.852100872799999</v>
+      </c>
+      <c r="P29">
+        <v>-14.8474179272</v>
+      </c>
+      <c r="Q29">
+        <v>1.9525820728</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09921008293979557</v>
+      </c>
+      <c r="T29">
+        <v>1.02143436458274</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.5770239154284764</v>
+      </c>
+      <c r="W29">
+        <v>0.3765933110043202</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-2.8010869680994</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1761035545172172</v>
+      </c>
+      <c r="C30">
+        <v>17.12465884134914</v>
+      </c>
+      <c r="D30">
+        <v>33.84865884134914</v>
+      </c>
+      <c r="E30">
+        <v>-28.436</v>
+      </c>
+      <c r="F30">
+        <v>21.364</v>
+      </c>
+      <c r="G30">
+        <v>4.64</v>
+      </c>
+      <c r="H30">
+        <v>26.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.02</v>
+      </c>
+      <c r="K30">
+        <v>16.8</v>
+      </c>
+      <c r="L30">
+        <v>-13.78</v>
+      </c>
+      <c r="M30">
+        <v>5.1017232</v>
+      </c>
+      <c r="N30">
+        <v>-18.8817232</v>
+      </c>
+      <c r="O30">
+        <v>-3.8896349792</v>
+      </c>
+      <c r="P30">
+        <v>-14.9920882208</v>
+      </c>
+      <c r="Q30">
+        <v>1.807911779199998</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.100049111869515</v>
+      </c>
+      <c r="T30">
+        <v>1.035620952979722</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.5564159184488879</v>
+      </c>
+      <c r="W30">
+        <v>0.3716721213255945</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-2.701048147810136</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1781035545172172</v>
+      </c>
+      <c r="C31">
+        <v>16.01199116015654</v>
+      </c>
+      <c r="D31">
+        <v>33.49899116015654</v>
+      </c>
+      <c r="E31">
+        <v>-27.673</v>
+      </c>
+      <c r="F31">
+        <v>22.127</v>
+      </c>
+      <c r="G31">
+        <v>4.64</v>
+      </c>
+      <c r="H31">
+        <v>26.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.02</v>
+      </c>
+      <c r="K31">
+        <v>16.8</v>
+      </c>
+      <c r="L31">
+        <v>-13.78</v>
+      </c>
+      <c r="M31">
+        <v>5.2839276</v>
+      </c>
+      <c r="N31">
+        <v>-19.0639276</v>
+      </c>
+      <c r="O31">
+        <v>-3.927169085599999</v>
+      </c>
+      <c r="P31">
+        <v>-15.1367585144</v>
+      </c>
+      <c r="Q31">
+        <v>1.6632414856</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1009117754169729</v>
+      </c>
+      <c r="T31">
+        <v>1.05020716358507</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.5372291626403056</v>
+      </c>
+      <c r="W31">
+        <v>0.367090324038505</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-2.607908556506338</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1801035545172172</v>
+      </c>
+      <c r="C32">
+        <v>14.90647397430703</v>
+      </c>
+      <c r="D32">
+        <v>33.15647397430703</v>
+      </c>
+      <c r="E32">
+        <v>-26.91</v>
+      </c>
+      <c r="F32">
+        <v>22.89</v>
+      </c>
+      <c r="G32">
+        <v>4.64</v>
+      </c>
+      <c r="H32">
+        <v>26.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.02</v>
+      </c>
+      <c r="K32">
+        <v>16.8</v>
+      </c>
+      <c r="L32">
+        <v>-13.78</v>
+      </c>
+      <c r="M32">
+        <v>5.466132</v>
+      </c>
+      <c r="N32">
+        <v>-19.246132</v>
+      </c>
+      <c r="O32">
+        <v>-3.964703192</v>
+      </c>
+      <c r="P32">
+        <v>-15.281428808</v>
+      </c>
+      <c r="Q32">
+        <v>1.518571191999998</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1017990864943582</v>
+      </c>
+      <c r="T32">
+        <v>1.065210123064857</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.5193215238856288</v>
+      </c>
+      <c r="W32">
+        <v>0.3628139799038882</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-2.520978271289461</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1821035545172172</v>
+      </c>
+      <c r="C33">
+        <v>13.80789016869593</v>
+      </c>
+      <c r="D33">
+        <v>32.82089016869593</v>
+      </c>
+      <c r="E33">
+        <v>-26.147</v>
+      </c>
+      <c r="F33">
+        <v>23.653</v>
+      </c>
+      <c r="G33">
+        <v>4.64</v>
+      </c>
+      <c r="H33">
+        <v>26.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.02</v>
+      </c>
+      <c r="K33">
+        <v>16.8</v>
+      </c>
+      <c r="L33">
+        <v>-13.78</v>
+      </c>
+      <c r="M33">
+        <v>5.6483364</v>
+      </c>
+      <c r="N33">
+        <v>-19.4283364</v>
+      </c>
+      <c r="O33">
+        <v>-4.002237298399999</v>
+      </c>
+      <c r="P33">
+        <v>-15.4260991016</v>
+      </c>
+      <c r="Q33">
+        <v>1.373900898400001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1027121167334069</v>
+      </c>
+      <c r="T33">
+        <v>1.080647950935362</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.5025692166635117</v>
+      </c>
+      <c r="W33">
+        <v>0.3588135289392467</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-2.439656391570445</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1841035545172172</v>
+      </c>
+      <c r="C34">
+        <v>12.71603133002049</v>
+      </c>
+      <c r="D34">
+        <v>32.49203133002049</v>
+      </c>
+      <c r="E34">
+        <v>-25.384</v>
+      </c>
+      <c r="F34">
+        <v>24.416</v>
+      </c>
+      <c r="G34">
+        <v>4.64</v>
+      </c>
+      <c r="H34">
+        <v>26.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.02</v>
+      </c>
+      <c r="K34">
+        <v>16.8</v>
+      </c>
+      <c r="L34">
+        <v>-13.78</v>
+      </c>
+      <c r="M34">
+        <v>5.830540800000001</v>
+      </c>
+      <c r="N34">
+        <v>-19.6105408</v>
+      </c>
+      <c r="O34">
+        <v>-4.0397714048</v>
+      </c>
+      <c r="P34">
+        <v>-15.5707693952</v>
+      </c>
+      <c r="Q34">
+        <v>1.229230604799998</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1036520008030158</v>
+      </c>
+      <c r="T34">
+        <v>1.096539832566765</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.4868639286427769</v>
+      </c>
+      <c r="W34">
+        <v>0.3550631061598952</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-2.363417129333869</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1861035545172172</v>
+      </c>
+      <c r="C35">
+        <v>11.63069731515298</v>
+      </c>
+      <c r="D35">
+        <v>32.16969731515297</v>
+      </c>
+      <c r="E35">
+        <v>-24.621</v>
+      </c>
+      <c r="F35">
+        <v>25.179</v>
+      </c>
+      <c r="G35">
+        <v>4.64</v>
+      </c>
+      <c r="H35">
+        <v>26.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.02</v>
+      </c>
+      <c r="K35">
+        <v>16.8</v>
+      </c>
+      <c r="L35">
+        <v>-13.78</v>
+      </c>
+      <c r="M35">
+        <v>6.0127452</v>
+      </c>
+      <c r="N35">
+        <v>-19.7927452</v>
+      </c>
+      <c r="O35">
+        <v>-4.0773055112</v>
+      </c>
+      <c r="P35">
+        <v>-15.7154396888</v>
+      </c>
+      <c r="Q35">
+        <v>1.084560311199997</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1046199411135086</v>
+      </c>
+      <c r="T35">
+        <v>1.112906098724477</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.4721104762596625</v>
+      </c>
+      <c r="W35">
+        <v>0.3515399817308074</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-2.291798428444964</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1881035545172172</v>
+      </c>
+      <c r="C36">
+        <v>10.55169584495292</v>
+      </c>
+      <c r="D36">
+        <v>31.85369584495293</v>
+      </c>
+      <c r="E36">
+        <v>-23.858</v>
+      </c>
+      <c r="F36">
+        <v>25.942</v>
+      </c>
+      <c r="G36">
+        <v>4.64</v>
+      </c>
+      <c r="H36">
+        <v>26.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.02</v>
+      </c>
+      <c r="K36">
+        <v>16.8</v>
+      </c>
+      <c r="L36">
+        <v>-13.78</v>
+      </c>
+      <c r="M36">
+        <v>6.1949496</v>
+      </c>
+      <c r="N36">
+        <v>-19.9749496</v>
+      </c>
+      <c r="O36">
+        <v>-4.114839617599999</v>
+      </c>
+      <c r="P36">
+        <v>-15.8601099824</v>
+      </c>
+      <c r="Q36">
+        <v>0.939890017599998</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1056172129485618</v>
+      </c>
+      <c r="T36">
+        <v>1.129768312341515</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.4582248740167312</v>
+      </c>
+      <c r="W36">
+        <v>0.3482240999151954</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-2.22439259231423</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1901035545172172</v>
+      </c>
+      <c r="C37">
+        <v>9.478842121786325</v>
+      </c>
+      <c r="D37">
+        <v>31.54384212178633</v>
+      </c>
+      <c r="E37">
+        <v>-23.095</v>
+      </c>
+      <c r="F37">
+        <v>26.705</v>
+      </c>
+      <c r="G37">
+        <v>4.64</v>
+      </c>
+      <c r="H37">
+        <v>26.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.02</v>
+      </c>
+      <c r="K37">
+        <v>16.8</v>
+      </c>
+      <c r="L37">
+        <v>-13.78</v>
+      </c>
+      <c r="M37">
+        <v>6.377154000000001</v>
+      </c>
+      <c r="N37">
+        <v>-20.157154</v>
+      </c>
+      <c r="O37">
+        <v>-4.152373723999999</v>
+      </c>
+      <c r="P37">
+        <v>-16.004780276</v>
+      </c>
+      <c r="Q37">
+        <v>0.795219723999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1066451700708473</v>
+      </c>
+      <c r="T37">
+        <v>1.147149363300615</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.4451327347591102</v>
+      </c>
+      <c r="W37">
+        <v>0.3450976970604756</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-2.160838518248108</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1921035545172172</v>
+      </c>
+      <c r="C38">
+        <v>8.411958469152957</v>
+      </c>
+      <c r="D38">
+        <v>31.23995846915295</v>
+      </c>
+      <c r="E38">
+        <v>-22.332</v>
+      </c>
+      <c r="F38">
+        <v>27.468</v>
+      </c>
+      <c r="G38">
+        <v>4.64</v>
+      </c>
+      <c r="H38">
+        <v>26.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.02</v>
+      </c>
+      <c r="K38">
+        <v>16.8</v>
+      </c>
+      <c r="L38">
+        <v>-13.78</v>
+      </c>
+      <c r="M38">
+        <v>6.5593584</v>
+      </c>
+      <c r="N38">
+        <v>-20.3393584</v>
+      </c>
+      <c r="O38">
+        <v>-4.189907830399999</v>
+      </c>
+      <c r="P38">
+        <v>-16.1494505696</v>
+      </c>
+      <c r="Q38">
+        <v>0.6505494303999981</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1077052508532043</v>
+      </c>
+      <c r="T38">
+        <v>1.165073572102187</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.4327679365713573</v>
+      </c>
+      <c r="W38">
+        <v>0.3421449832532401</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-2.100815226074551</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1941035545172172</v>
+      </c>
+      <c r="C39">
+        <v>7.350873991945274</v>
+      </c>
+      <c r="D39">
+        <v>30.94187399194528</v>
+      </c>
+      <c r="E39">
+        <v>-21.569</v>
+      </c>
+      <c r="F39">
+        <v>28.231</v>
+      </c>
+      <c r="G39">
+        <v>4.64</v>
+      </c>
+      <c r="H39">
+        <v>26.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.02</v>
+      </c>
+      <c r="K39">
+        <v>16.8</v>
+      </c>
+      <c r="L39">
+        <v>-13.78</v>
+      </c>
+      <c r="M39">
+        <v>6.7415628</v>
+      </c>
+      <c r="N39">
+        <v>-20.5215628</v>
+      </c>
+      <c r="O39">
+        <v>-4.227441936799999</v>
+      </c>
+      <c r="P39">
+        <v>-16.2941208632</v>
+      </c>
+      <c r="Q39">
+        <v>0.5058791367999973</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1087989849937314</v>
+      </c>
+      <c r="T39">
+        <v>1.183566803405397</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.4210715058532125</v>
+      </c>
+      <c r="W39">
+        <v>0.3393518755977472</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-2.044036436180644</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1961035545172172</v>
+      </c>
+      <c r="C40">
+        <v>6.295424255973984</v>
+      </c>
+      <c r="D40">
+        <v>30.64942425597398</v>
+      </c>
+      <c r="E40">
+        <v>-20.806</v>
+      </c>
+      <c r="F40">
+        <v>28.994</v>
+      </c>
+      <c r="G40">
+        <v>4.64</v>
+      </c>
+      <c r="H40">
+        <v>26.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.02</v>
+      </c>
+      <c r="K40">
+        <v>16.8</v>
+      </c>
+      <c r="L40">
+        <v>-13.78</v>
+      </c>
+      <c r="M40">
+        <v>6.9237672</v>
+      </c>
+      <c r="N40">
+        <v>-20.7037672</v>
+      </c>
+      <c r="O40">
+        <v>-4.2649760432</v>
+      </c>
+      <c r="P40">
+        <v>-16.4387911568</v>
+      </c>
+      <c r="Q40">
+        <v>0.3612088432</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.109928000880727</v>
+      </c>
+      <c r="T40">
+        <v>1.202656590557097</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.4099906767518122</v>
+      </c>
+      <c r="W40">
+        <v>0.3367057736083328</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-1.990246003649574</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1981035545172172</v>
+      </c>
+      <c r="C41">
+        <v>5.245450985497154</v>
+      </c>
+      <c r="D41">
+        <v>30.36245098549715</v>
+      </c>
+      <c r="E41">
+        <v>-20.043</v>
+      </c>
+      <c r="F41">
+        <v>29.757</v>
+      </c>
+      <c r="G41">
+        <v>4.64</v>
+      </c>
+      <c r="H41">
+        <v>26.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.02</v>
+      </c>
+      <c r="K41">
+        <v>16.8</v>
+      </c>
+      <c r="L41">
+        <v>-13.78</v>
+      </c>
+      <c r="M41">
+        <v>7.105971600000001</v>
+      </c>
+      <c r="N41">
+        <v>-20.8859716</v>
+      </c>
+      <c r="O41">
+        <v>-4.3025101496</v>
+      </c>
+      <c r="P41">
+        <v>-16.5834614504</v>
+      </c>
+      <c r="Q41">
+        <v>0.2165385495999992</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1110940336820504</v>
+      </c>
+      <c r="T41">
+        <v>1.222372272369508</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.3994780952966375</v>
+      </c>
+      <c r="W41">
+        <v>0.3341953691568371</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-1.939214054838046</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2001035545172172</v>
+      </c>
+      <c r="C42">
+        <v>4.200801777584356</v>
+      </c>
+      <c r="D42">
+        <v>30.08080177758436</v>
+      </c>
+      <c r="E42">
+        <v>-19.28</v>
+      </c>
+      <c r="F42">
+        <v>30.52</v>
+      </c>
+      <c r="G42">
+        <v>4.64</v>
+      </c>
+      <c r="H42">
+        <v>26.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.02</v>
+      </c>
+      <c r="K42">
+        <v>16.8</v>
+      </c>
+      <c r="L42">
+        <v>-13.78</v>
+      </c>
+      <c r="M42">
+        <v>7.288176</v>
+      </c>
+      <c r="N42">
+        <v>-21.068176</v>
+      </c>
+      <c r="O42">
+        <v>-4.340044256</v>
+      </c>
+      <c r="P42">
+        <v>-16.728131744</v>
+      </c>
+      <c r="Q42">
+        <v>0.07186825599999835</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1122989342434179</v>
+      </c>
+      <c r="T42">
+        <v>1.242745143575666</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.3894911429142216</v>
+      </c>
+      <c r="W42">
+        <v>0.3318104849279161</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-1.890733703467095</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2021035545172172</v>
+      </c>
+      <c r="C43">
+        <v>3.161329832232205</v>
+      </c>
+      <c r="D43">
+        <v>29.80432983223221</v>
+      </c>
+      <c r="E43">
+        <v>-18.517</v>
+      </c>
+      <c r="F43">
+        <v>31.283</v>
+      </c>
+      <c r="G43">
+        <v>4.64</v>
+      </c>
+      <c r="H43">
+        <v>26.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.02</v>
+      </c>
+      <c r="K43">
+        <v>16.8</v>
+      </c>
+      <c r="L43">
+        <v>-13.78</v>
+      </c>
+      <c r="M43">
+        <v>7.470380400000001</v>
+      </c>
+      <c r="N43">
+        <v>-21.2503804</v>
+      </c>
+      <c r="O43">
+        <v>-4.3775783624</v>
+      </c>
+      <c r="P43">
+        <v>-16.8728020376</v>
+      </c>
+      <c r="Q43">
+        <v>-0.07280203760000248</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1135446788916114</v>
+      </c>
+      <c r="T43">
+        <v>1.263808620585423</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.3799913589407039</v>
+      </c>
+      <c r="W43">
+        <v>0.3295419365150401</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-1.844618247284971</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2041035545172172</v>
+      </c>
+      <c r="C44">
+        <v>2.126893697227473</v>
+      </c>
+      <c r="D44">
+        <v>29.53289369722747</v>
+      </c>
+      <c r="E44">
+        <v>-17.754</v>
+      </c>
+      <c r="F44">
+        <v>32.046</v>
+      </c>
+      <c r="G44">
+        <v>4.64</v>
+      </c>
+      <c r="H44">
+        <v>26.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.02</v>
+      </c>
+      <c r="K44">
+        <v>16.8</v>
+      </c>
+      <c r="L44">
+        <v>-13.78</v>
+      </c>
+      <c r="M44">
+        <v>7.652584800000001</v>
+      </c>
+      <c r="N44">
+        <v>-21.4325848</v>
+      </c>
+      <c r="O44">
+        <v>-4.415112468799999</v>
+      </c>
+      <c r="P44">
+        <v>-17.0174723312</v>
+      </c>
+      <c r="Q44">
+        <v>-0.2174723311999998</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1148333802518117</v>
+      </c>
+      <c r="T44">
+        <v>1.28559842438862</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.370943945632592</v>
+      </c>
+      <c r="W44">
+        <v>0.327381414217063</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-1.800698765206757</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2061035545172172</v>
+      </c>
+      <c r="C45">
+        <v>1.09735702682601</v>
+      </c>
+      <c r="D45">
+        <v>29.26635702682601</v>
+      </c>
+      <c r="E45">
+        <v>-16.991</v>
+      </c>
+      <c r="F45">
+        <v>32.809</v>
+      </c>
+      <c r="G45">
+        <v>4.64</v>
+      </c>
+      <c r="H45">
+        <v>26.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.02</v>
+      </c>
+      <c r="K45">
+        <v>16.8</v>
+      </c>
+      <c r="L45">
+        <v>-13.78</v>
+      </c>
+      <c r="M45">
+        <v>7.834789199999999</v>
+      </c>
+      <c r="N45">
+        <v>-21.6147892</v>
+      </c>
+      <c r="O45">
+        <v>-4.452646575199999</v>
+      </c>
+      <c r="P45">
+        <v>-17.1621426248</v>
+      </c>
+      <c r="Q45">
+        <v>-0.3621426248000006</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1161672992035978</v>
+      </c>
+      <c r="T45">
+        <v>1.308152782711228</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.3623173422457875</v>
+      </c>
+      <c r="W45">
+        <v>0.3253213813282941</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-1.758822049736833</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2081035545172172</v>
+      </c>
+      <c r="C46">
+        <v>0.0725883533823577</v>
+      </c>
+      <c r="D46">
+        <v>29.00458835338236</v>
+      </c>
+      <c r="E46">
+        <v>-16.228</v>
+      </c>
+      <c r="F46">
+        <v>33.572</v>
+      </c>
+      <c r="G46">
+        <v>4.64</v>
+      </c>
+      <c r="H46">
+        <v>26.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.02</v>
+      </c>
+      <c r="K46">
+        <v>16.8</v>
+      </c>
+      <c r="L46">
+        <v>-13.78</v>
+      </c>
+      <c r="M46">
+        <v>8.016993599999999</v>
+      </c>
+      <c r="N46">
+        <v>-21.7969936</v>
+      </c>
+      <c r="O46">
+        <v>-4.490180681599999</v>
+      </c>
+      <c r="P46">
+        <v>-17.3068129184</v>
+      </c>
+      <c r="Q46">
+        <v>-0.5068129184000014</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1175488581179478</v>
+      </c>
+      <c r="T46">
+        <v>1.331512653831071</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.3540828571947469</v>
+      </c>
+      <c r="W46">
+        <v>0.3233549862981056</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-1.718848821333723</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2101035545172172</v>
+      </c>
+      <c r="C47">
+        <v>-0.9475391288734656</v>
+      </c>
+      <c r="D47">
+        <v>28.74746087112653</v>
+      </c>
+      <c r="E47">
+        <v>-15.465</v>
+      </c>
+      <c r="F47">
+        <v>34.335</v>
+      </c>
+      <c r="G47">
+        <v>4.64</v>
+      </c>
+      <c r="H47">
+        <v>26.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.02</v>
+      </c>
+      <c r="K47">
+        <v>16.8</v>
+      </c>
+      <c r="L47">
+        <v>-13.78</v>
+      </c>
+      <c r="M47">
+        <v>8.199198000000001</v>
+      </c>
+      <c r="N47">
+        <v>-21.979198</v>
+      </c>
+      <c r="O47">
+        <v>-4.527714788</v>
+      </c>
+      <c r="P47">
+        <v>-17.451483212</v>
+      </c>
+      <c r="Q47">
+        <v>-0.6514832120000023</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1189806555382741</v>
+      </c>
+      <c r="T47">
+        <v>1.355721974809818</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.3462143492570858</v>
+      </c>
+      <c r="W47">
+        <v>0.3214759866025921</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-1.68065218085964</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2121035545172172</v>
+      </c>
+      <c r="C48">
+        <v>-1.96314776865934</v>
+      </c>
+      <c r="D48">
+        <v>28.49485223134066</v>
+      </c>
+      <c r="E48">
+        <v>-14.702</v>
+      </c>
+      <c r="F48">
+        <v>35.098</v>
+      </c>
+      <c r="G48">
+        <v>4.64</v>
+      </c>
+      <c r="H48">
+        <v>26.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.02</v>
+      </c>
+      <c r="K48">
+        <v>16.8</v>
+      </c>
+      <c r="L48">
+        <v>-13.78</v>
+      </c>
+      <c r="M48">
+        <v>8.381402400000001</v>
+      </c>
+      <c r="N48">
+        <v>-22.1614024</v>
+      </c>
+      <c r="O48">
+        <v>-4.565248894399999</v>
+      </c>
+      <c r="P48">
+        <v>-17.5961535056</v>
+      </c>
+      <c r="Q48">
+        <v>-0.7961535055999995</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1204654824926866</v>
+      </c>
+      <c r="T48">
+        <v>1.380827937306296</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.3386879503601927</v>
+      </c>
+      <c r="W48">
+        <v>0.3196786825460141</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-1.64411626388443</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2141035545172172</v>
+      </c>
+      <c r="C49">
+        <v>-2.974355651759382</v>
+      </c>
+      <c r="D49">
+        <v>28.24664434824062</v>
+      </c>
+      <c r="E49">
+        <v>-13.93899999999999</v>
+      </c>
+      <c r="F49">
+        <v>35.861</v>
+      </c>
+      <c r="G49">
+        <v>4.64</v>
+      </c>
+      <c r="H49">
+        <v>26.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.02</v>
+      </c>
+      <c r="K49">
+        <v>16.8</v>
+      </c>
+      <c r="L49">
+        <v>-13.78</v>
+      </c>
+      <c r="M49">
+        <v>8.563606800000002</v>
+      </c>
+      <c r="N49">
+        <v>-22.3436068</v>
+      </c>
+      <c r="O49">
+        <v>-4.6027830008</v>
+      </c>
+      <c r="P49">
+        <v>-17.7408237992</v>
+      </c>
+      <c r="Q49">
+        <v>-0.9408237992000039</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.122006340652926</v>
+      </c>
+      <c r="T49">
+        <v>1.406881294613962</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.3314818237567842</v>
+      </c>
+      <c r="W49">
+        <v>0.3179578595131201</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-1.609135066780506</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2161035545172172</v>
+      </c>
+      <c r="C50">
+        <v>-3.981276785084866</v>
+      </c>
+      <c r="D50">
+        <v>28.00272321491513</v>
+      </c>
+      <c r="E50">
+        <v>-13.176</v>
+      </c>
+      <c r="F50">
+        <v>36.624</v>
+      </c>
+      <c r="G50">
+        <v>4.64</v>
+      </c>
+      <c r="H50">
+        <v>26.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.02</v>
+      </c>
+      <c r="K50">
+        <v>16.8</v>
+      </c>
+      <c r="L50">
+        <v>-13.78</v>
+      </c>
+      <c r="M50">
+        <v>8.745811199999999</v>
+      </c>
+      <c r="N50">
+        <v>-22.5258112</v>
+      </c>
+      <c r="O50">
+        <v>-4.640317107199999</v>
+      </c>
+      <c r="P50">
+        <v>-17.8854940928</v>
+      </c>
+      <c r="Q50">
+        <v>-1.085494092800001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1236064625885592</v>
+      </c>
+      <c r="T50">
+        <v>1.433936704125769</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.324575952428518</v>
+      </c>
+      <c r="W50">
+        <v>0.3163087374399302</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-1.575611419555913</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2181035545172172</v>
+      </c>
+      <c r="C51">
+        <v>-4.984021271279836</v>
+      </c>
+      <c r="D51">
+        <v>27.76297872872016</v>
+      </c>
+      <c r="E51">
+        <v>-12.413</v>
+      </c>
+      <c r="F51">
+        <v>37.387</v>
+      </c>
+      <c r="G51">
+        <v>4.64</v>
+      </c>
+      <c r="H51">
+        <v>26.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.02</v>
+      </c>
+      <c r="K51">
+        <v>16.8</v>
+      </c>
+      <c r="L51">
+        <v>-13.78</v>
+      </c>
+      <c r="M51">
+        <v>8.9280156</v>
+      </c>
+      <c r="N51">
+        <v>-22.7080156</v>
+      </c>
+      <c r="O51">
+        <v>-4.677851213599999</v>
+      </c>
+      <c r="P51">
+        <v>-18.0301643864</v>
+      </c>
+      <c r="Q51">
+        <v>-1.230164386400002</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1252693344040211</v>
+      </c>
+      <c r="T51">
+        <v>1.462053110089019</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.3179519533993646</v>
+      </c>
+      <c r="W51">
+        <v>0.3147269264717683</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-1.543456084462935</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2201035545172172</v>
+      </c>
+      <c r="C52">
+        <v>-5.982695474433712</v>
+      </c>
+      <c r="D52">
+        <v>27.52730452556629</v>
+      </c>
+      <c r="E52">
+        <v>-11.65</v>
+      </c>
+      <c r="F52">
+        <v>38.15</v>
+      </c>
+      <c r="G52">
+        <v>4.64</v>
+      </c>
+      <c r="H52">
+        <v>26.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.02</v>
+      </c>
+      <c r="K52">
+        <v>16.8</v>
+      </c>
+      <c r="L52">
+        <v>-13.78</v>
+      </c>
+      <c r="M52">
+        <v>9.11022</v>
+      </c>
+      <c r="N52">
+        <v>-22.89022</v>
+      </c>
+      <c r="O52">
+        <v>-4.715385319999999</v>
+      </c>
+      <c r="P52">
+        <v>-18.17483468</v>
+      </c>
+      <c r="Q52">
+        <v>-1.374834679999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1269987210921015</v>
+      </c>
+      <c r="T52">
+        <v>1.4912941722908</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.3115929143313773</v>
+      </c>
+      <c r="W52">
+        <v>0.3132083879423329</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-1.512586962773676</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2221035545172172</v>
+      </c>
+      <c r="C53">
+        <v>-6.977402177424835</v>
+      </c>
+      <c r="D53">
+        <v>27.29559782257516</v>
+      </c>
+      <c r="E53">
+        <v>-10.887</v>
+      </c>
+      <c r="F53">
+        <v>38.913</v>
+      </c>
+      <c r="G53">
+        <v>4.64</v>
+      </c>
+      <c r="H53">
+        <v>26.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.02</v>
+      </c>
+      <c r="K53">
+        <v>16.8</v>
+      </c>
+      <c r="L53">
+        <v>-13.78</v>
+      </c>
+      <c r="M53">
+        <v>9.2924244</v>
+      </c>
+      <c r="N53">
+        <v>-23.0724244</v>
+      </c>
+      <c r="O53">
+        <v>-4.7529194264</v>
+      </c>
+      <c r="P53">
+        <v>-18.3195049736</v>
+      </c>
+      <c r="Q53">
+        <v>-1.519504973600004</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1287986949919403</v>
+      </c>
+      <c r="T53">
+        <v>1.52172874723551</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.3054832493444875</v>
+      </c>
+      <c r="W53">
+        <v>0.3117493999434636</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-1.482928394876153</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2241035545172172</v>
+      </c>
+      <c r="C54">
+        <v>-7.968240731383634</v>
+      </c>
+      <c r="D54">
+        <v>27.06775926861637</v>
+      </c>
+      <c r="E54">
+        <v>-10.124</v>
+      </c>
+      <c r="F54">
+        <v>39.676</v>
+      </c>
+      <c r="G54">
+        <v>4.64</v>
+      </c>
+      <c r="H54">
+        <v>26.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.02</v>
+      </c>
+      <c r="K54">
+        <v>16.8</v>
+      </c>
+      <c r="L54">
+        <v>-13.78</v>
+      </c>
+      <c r="M54">
+        <v>9.474628800000001</v>
+      </c>
+      <c r="N54">
+        <v>-23.2546288</v>
+      </c>
+      <c r="O54">
+        <v>-4.7904535328</v>
+      </c>
+      <c r="P54">
+        <v>-18.4641752672</v>
+      </c>
+      <c r="Q54">
+        <v>-1.664175267200001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1306736678042724</v>
+      </c>
+      <c r="T54">
+        <v>1.553431429469583</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.2996085714724781</v>
+      </c>
+      <c r="W54">
+        <v>0.3103465268676278</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-1.454410541128535</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2261035545172172</v>
+      </c>
+      <c r="C55">
+        <v>-8.955307197732456</v>
+      </c>
+      <c r="D55">
+        <v>26.84369280226754</v>
+      </c>
+      <c r="E55">
+        <v>-9.360999999999997</v>
+      </c>
+      <c r="F55">
+        <v>40.439</v>
+      </c>
+      <c r="G55">
+        <v>4.64</v>
+      </c>
+      <c r="H55">
+        <v>26.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.02</v>
+      </c>
+      <c r="K55">
+        <v>16.8</v>
+      </c>
+      <c r="L55">
+        <v>-13.78</v>
+      </c>
+      <c r="M55">
+        <v>9.656833200000001</v>
+      </c>
+      <c r="N55">
+        <v>-23.4368332</v>
+      </c>
+      <c r="O55">
+        <v>-4.8279876392</v>
+      </c>
+      <c r="P55">
+        <v>-18.6088455608</v>
+      </c>
+      <c r="Q55">
+        <v>-1.808845560800002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.132628426693725</v>
+      </c>
+      <c r="T55">
+        <v>1.586483162011489</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.293955579557903</v>
+      </c>
+      <c r="W55">
+        <v>0.3089965923984273</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-1.426968832805355</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2281035545172173</v>
+      </c>
+      <c r="C56">
+        <v>-9.938694483228407</v>
+      </c>
+      <c r="D56">
+        <v>26.62330551677159</v>
+      </c>
+      <c r="E56">
+        <v>-8.597999999999999</v>
+      </c>
+      <c r="F56">
+        <v>41.202</v>
+      </c>
+      <c r="G56">
+        <v>4.64</v>
+      </c>
+      <c r="H56">
+        <v>26.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.02</v>
+      </c>
+      <c r="K56">
+        <v>16.8</v>
+      </c>
+      <c r="L56">
+        <v>-13.78</v>
+      </c>
+      <c r="M56">
+        <v>9.839037599999999</v>
+      </c>
+      <c r="N56">
+        <v>-23.6190376</v>
+      </c>
+      <c r="O56">
+        <v>-4.865521745599999</v>
+      </c>
+      <c r="P56">
+        <v>-18.7535158544</v>
+      </c>
+      <c r="Q56">
+        <v>-1.953515854399999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1346681751001104</v>
+      </c>
+      <c r="T56">
+        <v>1.620971926403043</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.2885119577142382</v>
+      </c>
+      <c r="W56">
+        <v>0.3076966555021601</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-1.4005434840497</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2301035545172172</v>
+      </c>
+      <c r="C57">
+        <v>-10.91849246840815</v>
+      </c>
+      <c r="D57">
+        <v>26.40650753159186</v>
+      </c>
+      <c r="E57">
+        <v>-7.834999999999994</v>
+      </c>
+      <c r="F57">
+        <v>41.965</v>
+      </c>
+      <c r="G57">
+        <v>4.64</v>
+      </c>
+      <c r="H57">
+        <v>26.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.02</v>
+      </c>
+      <c r="K57">
+        <v>16.8</v>
+      </c>
+      <c r="L57">
+        <v>-13.78</v>
+      </c>
+      <c r="M57">
+        <v>10.021242</v>
+      </c>
+      <c r="N57">
+        <v>-23.801242</v>
+      </c>
+      <c r="O57">
+        <v>-4.903055852</v>
+      </c>
+      <c r="P57">
+        <v>-18.898186148</v>
+      </c>
+      <c r="Q57">
+        <v>-2.098186148</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1367985789912239</v>
+      </c>
+      <c r="T57">
+        <v>1.656993524767555</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.2832662857557975</v>
+      </c>
+      <c r="W57">
+        <v>0.3064439890384845</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-1.375079057066978</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2321035545172172</v>
+      </c>
+      <c r="C58">
+        <v>-11.89478812980777</v>
+      </c>
+      <c r="D58">
+        <v>26.19321187019223</v>
+      </c>
+      <c r="E58">
+        <v>-7.071999999999996</v>
+      </c>
+      <c r="F58">
+        <v>42.728</v>
+      </c>
+      <c r="G58">
+        <v>4.64</v>
+      </c>
+      <c r="H58">
+        <v>26.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.02</v>
+      </c>
+      <c r="K58">
+        <v>16.8</v>
+      </c>
+      <c r="L58">
+        <v>-13.78</v>
+      </c>
+      <c r="M58">
+        <v>10.2034464</v>
+      </c>
+      <c r="N58">
+        <v>-23.9834464</v>
+      </c>
+      <c r="O58">
+        <v>-4.940589958399999</v>
+      </c>
+      <c r="P58">
+        <v>-19.0428564416</v>
+      </c>
+      <c r="Q58">
+        <v>-2.242856441600001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1390258194228426</v>
+      </c>
+      <c r="T58">
+        <v>1.694652468512272</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.278207959224444</v>
+      </c>
+      <c r="W58">
+        <v>0.3052360606627972</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-1.350524073905068</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2341035545172172</v>
+      </c>
+      <c r="C59">
+        <v>-12.86766565630668</v>
+      </c>
+      <c r="D59">
+        <v>25.98333434369332</v>
+      </c>
+      <c r="E59">
+        <v>-6.308999999999997</v>
+      </c>
+      <c r="F59">
+        <v>43.491</v>
+      </c>
+      <c r="G59">
+        <v>4.64</v>
+      </c>
+      <c r="H59">
+        <v>26.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.02</v>
+      </c>
+      <c r="K59">
+        <v>16.8</v>
+      </c>
+      <c r="L59">
+        <v>-13.78</v>
+      </c>
+      <c r="M59">
+        <v>10.3856508</v>
+      </c>
+      <c r="N59">
+        <v>-24.1656508</v>
+      </c>
+      <c r="O59">
+        <v>-4.978124064799999</v>
+      </c>
+      <c r="P59">
+        <v>-19.1875267352</v>
+      </c>
+      <c r="Q59">
+        <v>-2.387526735200002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1413566524326762</v>
+      </c>
+      <c r="T59">
+        <v>1.734062991035814</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.2733271178345414</v>
+      </c>
+      <c r="W59">
+        <v>0.3040705157388885</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-1.326830669099716</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2361035545172172</v>
+      </c>
+      <c r="C60">
+        <v>-13.83720655992276</v>
+      </c>
+      <c r="D60">
+        <v>25.77679344007724</v>
+      </c>
+      <c r="E60">
+        <v>-5.545999999999999</v>
+      </c>
+      <c r="F60">
+        <v>44.254</v>
+      </c>
+      <c r="G60">
+        <v>4.64</v>
+      </c>
+      <c r="H60">
+        <v>26.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.02</v>
+      </c>
+      <c r="K60">
+        <v>16.8</v>
+      </c>
+      <c r="L60">
+        <v>-13.78</v>
+      </c>
+      <c r="M60">
+        <v>10.5678552</v>
+      </c>
+      <c r="N60">
+        <v>-24.3478552</v>
+      </c>
+      <c r="O60">
+        <v>-5.015658171199999</v>
+      </c>
+      <c r="P60">
+        <v>-19.3321970288</v>
+      </c>
+      <c r="Q60">
+        <v>-2.532197028800002</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.143798477490597</v>
+      </c>
+      <c r="T60">
+        <v>1.775350205108095</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.2686145813201528</v>
+      </c>
+      <c r="W60">
+        <v>0.3029451620192525</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-1.303954278253169</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2381035545172172</v>
+      </c>
+      <c r="C61">
+        <v>-14.8034897813648</v>
+      </c>
+      <c r="D61">
+        <v>25.57351021863519</v>
+      </c>
+      <c r="E61">
+        <v>-4.783000000000001</v>
+      </c>
+      <c r="F61">
+        <v>45.017</v>
+      </c>
+      <c r="G61">
+        <v>4.64</v>
+      </c>
+      <c r="H61">
+        <v>26.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.02</v>
+      </c>
+      <c r="K61">
+        <v>16.8</v>
+      </c>
+      <c r="L61">
+        <v>-13.78</v>
+      </c>
+      <c r="M61">
+        <v>10.7500596</v>
+      </c>
+      <c r="N61">
+        <v>-24.5300596</v>
+      </c>
+      <c r="O61">
+        <v>-5.053192277599999</v>
+      </c>
+      <c r="P61">
+        <v>-19.4768673224</v>
+      </c>
+      <c r="Q61">
+        <v>-2.676867322400003</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1463594159659775</v>
+      </c>
+      <c r="T61">
+        <v>1.818651429622926</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.2640617918062519</v>
+      </c>
+      <c r="W61">
+        <v>0.301857955883333</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-1.281853358282777</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2401035545172172</v>
+      </c>
+      <c r="C62">
+        <v>-15.76659179062968</v>
+      </c>
+      <c r="D62">
+        <v>25.37340820937032</v>
+      </c>
+      <c r="E62">
+        <v>-4.020000000000003</v>
+      </c>
+      <c r="F62">
+        <v>45.77999999999999</v>
+      </c>
+      <c r="G62">
+        <v>4.64</v>
+      </c>
+      <c r="H62">
+        <v>26.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.02</v>
+      </c>
+      <c r="K62">
+        <v>16.8</v>
+      </c>
+      <c r="L62">
+        <v>-13.78</v>
+      </c>
+      <c r="M62">
+        <v>10.932264</v>
+      </c>
+      <c r="N62">
+        <v>-24.712264</v>
+      </c>
+      <c r="O62">
+        <v>-5.090726383999999</v>
+      </c>
+      <c r="P62">
+        <v>-19.621537616</v>
+      </c>
+      <c r="Q62">
+        <v>-2.821537616000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1490484013651269</v>
+      </c>
+      <c r="T62">
+        <v>1.864117715363499</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.2596607619428144</v>
+      </c>
+      <c r="W62">
+        <v>0.3008069899519441</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-1.26048913564473</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2421035545172172</v>
+      </c>
+      <c r="C63">
+        <v>-16.72658668291322</v>
+      </c>
+      <c r="D63">
+        <v>25.17641331708678</v>
+      </c>
+      <c r="E63">
+        <v>-3.256999999999998</v>
+      </c>
+      <c r="F63">
+        <v>46.543</v>
+      </c>
+      <c r="G63">
+        <v>4.64</v>
+      </c>
+      <c r="H63">
+        <v>26.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.02</v>
+      </c>
+      <c r="K63">
+        <v>16.8</v>
+      </c>
+      <c r="L63">
+        <v>-13.78</v>
+      </c>
+      <c r="M63">
+        <v>11.1144684</v>
+      </c>
+      <c r="N63">
+        <v>-24.8944684</v>
+      </c>
+      <c r="O63">
+        <v>-5.128260490399999</v>
+      </c>
+      <c r="P63">
+        <v>-19.7662079096</v>
+      </c>
+      <c r="Q63">
+        <v>-2.966207909600001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1518752834514122</v>
+      </c>
+      <c r="T63">
+        <v>1.911915605501025</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.2554040281404731</v>
+      </c>
+      <c r="W63">
+        <v>0.299790481919945</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-1.239825379322685</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2441035545172172</v>
+      </c>
+      <c r="C64">
+        <v>-17.68354627008783</v>
+      </c>
+      <c r="D64">
+        <v>24.98245372991216</v>
+      </c>
+      <c r="E64">
+        <v>-2.494</v>
+      </c>
+      <c r="F64">
+        <v>47.306</v>
+      </c>
+      <c r="G64">
+        <v>4.64</v>
+      </c>
+      <c r="H64">
+        <v>26.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.02</v>
+      </c>
+      <c r="K64">
+        <v>16.8</v>
+      </c>
+      <c r="L64">
+        <v>-13.78</v>
+      </c>
+      <c r="M64">
+        <v>11.2966728</v>
+      </c>
+      <c r="N64">
+        <v>-25.0766728</v>
+      </c>
+      <c r="O64">
+        <v>-5.165794596799999</v>
+      </c>
+      <c r="P64">
+        <v>-19.9108782032</v>
+      </c>
+      <c r="Q64">
+        <v>-3.110878203200002</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1548509488053967</v>
+      </c>
+      <c r="T64">
+        <v>1.962229174066842</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.2512846083317559</v>
+      </c>
+      <c r="W64">
+        <v>0.2988067644696233</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-1.219828195785223</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2461035545172172</v>
+      </c>
+      <c r="C65">
+        <v>-18.63754016798394</v>
+      </c>
+      <c r="D65">
+        <v>24.79145983201606</v>
+      </c>
+      <c r="E65">
+        <v>-1.731000000000002</v>
+      </c>
+      <c r="F65">
+        <v>48.069</v>
+      </c>
+      <c r="G65">
+        <v>4.64</v>
+      </c>
+      <c r="H65">
+        <v>26.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.02</v>
+      </c>
+      <c r="K65">
+        <v>16.8</v>
+      </c>
+      <c r="L65">
+        <v>-13.78</v>
+      </c>
+      <c r="M65">
+        <v>11.4788772</v>
+      </c>
+      <c r="N65">
+        <v>-25.2588772</v>
+      </c>
+      <c r="O65">
+        <v>-5.2033287032</v>
+      </c>
+      <c r="P65">
+        <v>-20.0555484968</v>
+      </c>
+      <c r="Q65">
+        <v>-3.255548496799999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1579874609352723</v>
+      </c>
+      <c r="T65">
+        <v>2.015262394987567</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.2472959637550613</v>
+      </c>
+      <c r="W65">
+        <v>0.2978542761447087</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-1.200465843471172</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2481035545172172</v>
+      </c>
+      <c r="C66">
+        <v>-19.5886358796981</v>
+      </c>
+      <c r="D66">
+        <v>24.6033641203019</v>
+      </c>
+      <c r="E66">
+        <v>-0.9679999999999964</v>
+      </c>
+      <c r="F66">
+        <v>48.832</v>
+      </c>
+      <c r="G66">
+        <v>4.64</v>
+      </c>
+      <c r="H66">
+        <v>26.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.02</v>
+      </c>
+      <c r="K66">
+        <v>16.8</v>
+      </c>
+      <c r="L66">
+        <v>-13.78</v>
+      </c>
+      <c r="M66">
+        <v>11.6610816</v>
+      </c>
+      <c r="N66">
+        <v>-25.4410816</v>
+      </c>
+      <c r="O66">
+        <v>-5.240862809599999</v>
+      </c>
+      <c r="P66">
+        <v>-20.2002187904</v>
+      </c>
+      <c r="Q66">
+        <v>-3.400218790400004</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1612982237390299</v>
+      </c>
+      <c r="T66">
+        <v>2.071241905959444</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.2434319643213885</v>
+      </c>
+      <c r="W66">
+        <v>0.2969315530799476</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-1.181708564666935</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2501035545172172</v>
+      </c>
+      <c r="C67">
+        <v>-20.53689887513726</v>
+      </c>
+      <c r="D67">
+        <v>24.41810112486273</v>
+      </c>
+      <c r="E67">
+        <v>-0.2049999999999983</v>
+      </c>
+      <c r="F67">
+        <v>49.595</v>
+      </c>
+      <c r="G67">
+        <v>4.64</v>
+      </c>
+      <c r="H67">
+        <v>26.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.02</v>
+      </c>
+      <c r="K67">
+        <v>16.8</v>
+      </c>
+      <c r="L67">
+        <v>-13.78</v>
+      </c>
+      <c r="M67">
+        <v>11.843286</v>
+      </c>
+      <c r="N67">
+        <v>-25.623286</v>
+      </c>
+      <c r="O67">
+        <v>-5.278396915999999</v>
+      </c>
+      <c r="P67">
+        <v>-20.344889084</v>
+      </c>
+      <c r="Q67">
+        <v>-3.544889084000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1647981729887165</v>
+      </c>
+      <c r="T67">
+        <v>2.130420246129714</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.2396868571779825</v>
+      </c>
+      <c r="W67">
+        <v>0.2960372214941022</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-1.163528432902828</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2521035545172172</v>
+      </c>
+      <c r="C68">
+        <v>-21.4823926669962</v>
+      </c>
+      <c r="D68">
+        <v>24.2356073330038</v>
+      </c>
+      <c r="E68">
+        <v>0.5579999999999998</v>
+      </c>
+      <c r="F68">
+        <v>50.358</v>
+      </c>
+      <c r="G68">
+        <v>4.64</v>
+      </c>
+      <c r="H68">
+        <v>26.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.02</v>
+      </c>
+      <c r="K68">
+        <v>16.8</v>
+      </c>
+      <c r="L68">
+        <v>-13.78</v>
+      </c>
+      <c r="M68">
+        <v>12.0254904</v>
+      </c>
+      <c r="N68">
+        <v>-25.8054904</v>
+      </c>
+      <c r="O68">
+        <v>-5.3159310224</v>
+      </c>
+      <c r="P68">
+        <v>-20.4895593776</v>
+      </c>
+      <c r="Q68">
+        <v>-3.689559377600002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1685040016060317</v>
+      </c>
+      <c r="T68">
+        <v>2.193079665133529</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.2360552381298312</v>
+      </c>
+      <c r="W68">
+        <v>0.2951699908654037</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-1.145899214222482</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2541035545172172</v>
+      </c>
+      <c r="C69">
+        <v>-22.42517888335301</v>
+      </c>
+      <c r="D69">
+        <v>24.05582111664699</v>
+      </c>
+      <c r="E69">
+        <v>1.321000000000005</v>
+      </c>
+      <c r="F69">
+        <v>51.121</v>
+      </c>
+      <c r="G69">
+        <v>4.64</v>
+      </c>
+      <c r="H69">
+        <v>26.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.02</v>
+      </c>
+      <c r="K69">
+        <v>16.8</v>
+      </c>
+      <c r="L69">
+        <v>-13.78</v>
+      </c>
+      <c r="M69">
+        <v>12.2076948</v>
+      </c>
+      <c r="N69">
+        <v>-25.9876948</v>
+      </c>
+      <c r="O69">
+        <v>-5.353465128799999</v>
+      </c>
+      <c r="P69">
+        <v>-20.6342296712</v>
+      </c>
+      <c r="Q69">
+        <v>-3.834229671199999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1724344258971235</v>
+      </c>
+      <c r="T69">
+        <v>2.25953662468303</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.2325320256204308</v>
+      </c>
+      <c r="W69">
+        <v>0.2943286477181589</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-1.128796240875878</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2561035545172172</v>
+      </c>
+      <c r="C70">
+        <v>-23.36531733705742</v>
+      </c>
+      <c r="D70">
+        <v>23.87868266294258</v>
+      </c>
+      <c r="E70">
+        <v>2.084000000000003</v>
+      </c>
+      <c r="F70">
+        <v>51.884</v>
+      </c>
+      <c r="G70">
+        <v>4.64</v>
+      </c>
+      <c r="H70">
+        <v>26.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.02</v>
+      </c>
+      <c r="K70">
+        <v>16.8</v>
+      </c>
+      <c r="L70">
+        <v>-13.78</v>
+      </c>
+      <c r="M70">
+        <v>12.3898992</v>
+      </c>
+      <c r="N70">
+        <v>-26.1698992</v>
+      </c>
+      <c r="O70">
+        <v>-5.3909992352</v>
+      </c>
+      <c r="P70">
+        <v>-20.7788999648</v>
+      </c>
+      <c r="Q70">
+        <v>-3.978899964800004</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1766105017064087</v>
+      </c>
+      <c r="T70">
+        <v>2.330147144204375</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.2291124370083656</v>
+      </c>
+      <c r="W70">
+        <v>0.2935120499575977</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-1.112196296157115</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2581035545172172</v>
+      </c>
+      <c r="C71">
+        <v>-24.30286609207565</v>
+      </c>
+      <c r="D71">
+        <v>23.70413390792436</v>
+      </c>
+      <c r="E71">
+        <v>2.847000000000008</v>
+      </c>
+      <c r="F71">
+        <v>52.64700000000001</v>
+      </c>
+      <c r="G71">
+        <v>4.64</v>
+      </c>
+      <c r="H71">
+        <v>26.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.02</v>
+      </c>
+      <c r="K71">
+        <v>16.8</v>
+      </c>
+      <c r="L71">
+        <v>-13.78</v>
+      </c>
+      <c r="M71">
+        <v>12.5721036</v>
+      </c>
+      <c r="N71">
+        <v>-26.3521036</v>
+      </c>
+      <c r="O71">
+        <v>-5.4285333416</v>
+      </c>
+      <c r="P71">
+        <v>-20.92357025840001</v>
+      </c>
+      <c r="Q71">
+        <v>-4.123570258400004</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1810560017614541</v>
+      </c>
+      <c r="T71">
+        <v>2.405313181114193</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.2257919669067951</v>
+      </c>
+      <c r="W71">
+        <v>0.2927191216973427</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-1.096077509256287</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2601035545172172</v>
+      </c>
+      <c r="C72">
+        <v>-25.23788152694665</v>
+      </c>
+      <c r="D72">
+        <v>23.53211847305335</v>
+      </c>
+      <c r="E72">
+        <v>3.610000000000007</v>
+      </c>
+      <c r="F72">
+        <v>53.41</v>
+      </c>
+      <c r="G72">
+        <v>4.64</v>
+      </c>
+      <c r="H72">
+        <v>26.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.02</v>
+      </c>
+      <c r="K72">
+        <v>16.8</v>
+      </c>
+      <c r="L72">
+        <v>-13.78</v>
+      </c>
+      <c r="M72">
+        <v>12.754308</v>
+      </c>
+      <c r="N72">
+        <v>-26.534308</v>
+      </c>
+      <c r="O72">
+        <v>-5.466067448</v>
+      </c>
+      <c r="P72">
+        <v>-21.068240552</v>
+      </c>
+      <c r="Q72">
+        <v>-4.268240552000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1857978684868359</v>
+      </c>
+      <c r="T72">
+        <v>2.485490287151333</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.2225663673795551</v>
+      </c>
+      <c r="W72">
+        <v>0.2919488485302378</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-1.080419259124054</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2621035545172172</v>
+      </c>
+      <c r="C73">
+        <v>-26.17041839549533</v>
+      </c>
+      <c r="D73">
+        <v>23.36258160450467</v>
+      </c>
+      <c r="E73">
+        <v>4.372999999999998</v>
+      </c>
+      <c r="F73">
+        <v>54.17299999999999</v>
+      </c>
+      <c r="G73">
+        <v>4.64</v>
+      </c>
+      <c r="H73">
+        <v>26.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.02</v>
+      </c>
+      <c r="K73">
+        <v>16.8</v>
+      </c>
+      <c r="L73">
+        <v>-13.78</v>
+      </c>
+      <c r="M73">
+        <v>12.9365124</v>
+      </c>
+      <c r="N73">
+        <v>-26.7165124</v>
+      </c>
+      <c r="O73">
+        <v>-5.503601554399999</v>
+      </c>
+      <c r="P73">
+        <v>-21.2129108456</v>
+      </c>
+      <c r="Q73">
+        <v>-4.412910845599999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1908667605036233</v>
+      </c>
+      <c r="T73">
+        <v>2.57119684877724</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.219431629810829</v>
+      </c>
+      <c r="W73">
+        <v>0.291200273198826</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-1.065202086460335</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2641035545172172</v>
+      </c>
+      <c r="C74">
+        <v>-27.10052988494007</v>
+      </c>
+      <c r="D74">
+        <v>23.19547011505993</v>
+      </c>
+      <c r="E74">
+        <v>5.135999999999996</v>
+      </c>
+      <c r="F74">
+        <v>54.93599999999999</v>
+      </c>
+      <c r="G74">
+        <v>4.64</v>
+      </c>
+      <c r="H74">
+        <v>26.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.02</v>
+      </c>
+      <c r="K74">
+        <v>16.8</v>
+      </c>
+      <c r="L74">
+        <v>-13.78</v>
+      </c>
+      <c r="M74">
+        <v>13.1187168</v>
+      </c>
+      <c r="N74">
+        <v>-26.8987168</v>
+      </c>
+      <c r="O74">
+        <v>-5.541135660799999</v>
+      </c>
+      <c r="P74">
+        <v>-21.3575811392</v>
+      </c>
+      <c r="Q74">
+        <v>-4.557581139200003</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1962977162358956</v>
+      </c>
+      <c r="T74">
+        <v>2.663025307662142</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.2163839682856787</v>
+      </c>
+      <c r="W74">
+        <v>0.2904724916266201</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-1.050407613037275</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2661035545172172</v>
+      </c>
+      <c r="C75">
+        <v>-28.02826767152408</v>
+      </c>
+      <c r="D75">
+        <v>23.03073232847591</v>
+      </c>
+      <c r="E75">
+        <v>5.899000000000001</v>
+      </c>
+      <c r="F75">
+        <v>55.699</v>
+      </c>
+      <c r="G75">
+        <v>4.64</v>
+      </c>
+      <c r="H75">
+        <v>26.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.02</v>
+      </c>
+      <c r="K75">
+        <v>16.8</v>
+      </c>
+      <c r="L75">
+        <v>-13.78</v>
+      </c>
+      <c r="M75">
+        <v>13.3009212</v>
+      </c>
+      <c r="N75">
+        <v>-27.0809212</v>
+      </c>
+      <c r="O75">
+        <v>-5.578669767199998</v>
+      </c>
+      <c r="P75">
+        <v>-21.5022514328</v>
+      </c>
+      <c r="Q75">
+        <v>-4.702251432800001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2021309649853732</v>
+      </c>
+      <c r="T75">
+        <v>2.761655874612592</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.2134198043365598</v>
+      </c>
+      <c r="W75">
+        <v>0.2897646492755705</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-1.036018467653203</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2681035545172172</v>
+      </c>
+      <c r="C76">
+        <v>-28.953681973793</v>
+      </c>
+      <c r="D76">
+        <v>22.868318026207</v>
+      </c>
+      <c r="E76">
+        <v>6.661999999999999</v>
+      </c>
+      <c r="F76">
+        <v>56.462</v>
+      </c>
+      <c r="G76">
+        <v>4.64</v>
+      </c>
+      <c r="H76">
+        <v>26.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.02</v>
+      </c>
+      <c r="K76">
+        <v>16.8</v>
+      </c>
+      <c r="L76">
+        <v>-13.78</v>
+      </c>
+      <c r="M76">
+        <v>13.4831256</v>
+      </c>
+      <c r="N76">
+        <v>-27.2631256</v>
+      </c>
+      <c r="O76">
+        <v>-5.616203873599999</v>
+      </c>
+      <c r="P76">
+        <v>-21.6469217264</v>
+      </c>
+      <c r="Q76">
+        <v>-4.846921726400002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2084129251771183</v>
+      </c>
+      <c r="T76">
+        <v>2.867873408251537</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.2105357529266063</v>
+      </c>
+      <c r="W76">
+        <v>0.2890759377988736</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-1.022018218090322</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2701035545172172</v>
+      </c>
+      <c r="C77">
+        <v>-29.87682160363375</v>
+      </c>
+      <c r="D77">
+        <v>22.70817839636625</v>
+      </c>
+      <c r="E77">
+        <v>7.424999999999997</v>
+      </c>
+      <c r="F77">
+        <v>57.22499999999999</v>
+      </c>
+      <c r="G77">
+        <v>4.64</v>
+      </c>
+      <c r="H77">
+        <v>26.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.02</v>
+      </c>
+      <c r="K77">
+        <v>16.8</v>
+      </c>
+      <c r="L77">
+        <v>-13.78</v>
+      </c>
+      <c r="M77">
+        <v>13.66533</v>
+      </c>
+      <c r="N77">
+        <v>-27.44533</v>
+      </c>
+      <c r="O77">
+        <v>-5.653737979999999</v>
+      </c>
+      <c r="P77">
+        <v>-21.79159202</v>
+      </c>
+      <c r="Q77">
+        <v>-4.991592019999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.215197442184203</v>
+      </c>
+      <c r="T77">
+        <v>2.982588344581599</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.2077286095542515</v>
+      </c>
+      <c r="W77">
+        <v>0.2884055919615552</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-1.008391308515784</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2721035545172172</v>
+      </c>
+      <c r="C78">
+        <v>-30.79773401518412</v>
+      </c>
+      <c r="D78">
+        <v>22.55026598481588</v>
+      </c>
+      <c r="E78">
+        <v>8.188000000000002</v>
+      </c>
+      <c r="F78">
+        <v>57.988</v>
+      </c>
+      <c r="G78">
+        <v>4.64</v>
+      </c>
+      <c r="H78">
+        <v>26.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.02</v>
+      </c>
+      <c r="K78">
+        <v>16.8</v>
+      </c>
+      <c r="L78">
+        <v>-13.78</v>
+      </c>
+      <c r="M78">
+        <v>13.8475344</v>
+      </c>
+      <c r="N78">
+        <v>-27.6275344</v>
+      </c>
+      <c r="O78">
+        <v>-5.6912720864</v>
+      </c>
+      <c r="P78">
+        <v>-21.9362623136</v>
+      </c>
+      <c r="Q78">
+        <v>-5.136262313600003</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2225473356085448</v>
+      </c>
+      <c r="T78">
+        <v>3.106862858939166</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.2049953383759061</v>
+      </c>
+      <c r="W78">
+        <v>0.2877528868041664</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.995123001824787</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2741035545172172</v>
+      </c>
+      <c r="C79">
+        <v>-31.71646535171548</v>
+      </c>
+      <c r="D79">
+        <v>22.39453464828451</v>
+      </c>
+      <c r="E79">
+        <v>8.951000000000001</v>
+      </c>
+      <c r="F79">
+        <v>58.751</v>
+      </c>
+      <c r="G79">
+        <v>4.64</v>
+      </c>
+      <c r="H79">
+        <v>26.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.02</v>
+      </c>
+      <c r="K79">
+        <v>16.8</v>
+      </c>
+      <c r="L79">
+        <v>-13.78</v>
+      </c>
+      <c r="M79">
+        <v>14.0297388</v>
+      </c>
+      <c r="N79">
+        <v>-27.8097388</v>
+      </c>
+      <c r="O79">
+        <v>-5.7288061928</v>
+      </c>
+      <c r="P79">
+        <v>-22.0809326072</v>
+      </c>
+      <c r="Q79">
+        <v>-5.2809326072</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2305363502002207</v>
+      </c>
+      <c r="T79">
+        <v>3.241943852806086</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.2023330612541411</v>
+      </c>
+      <c r="W79">
+        <v>0.2871171350274889</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.9821993264764131</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2761035545172172</v>
+      </c>
+      <c r="C80">
+        <v>-32.63306049058642</v>
+      </c>
+      <c r="D80">
+        <v>22.24093950941358</v>
+      </c>
+      <c r="E80">
+        <v>9.714000000000006</v>
+      </c>
+      <c r="F80">
+        <v>59.514</v>
+      </c>
+      <c r="G80">
+        <v>4.64</v>
+      </c>
+      <c r="H80">
+        <v>26.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.02</v>
+      </c>
+      <c r="K80">
+        <v>16.8</v>
+      </c>
+      <c r="L80">
+        <v>-13.78</v>
+      </c>
+      <c r="M80">
+        <v>14.2119432</v>
+      </c>
+      <c r="N80">
+        <v>-27.9919432</v>
+      </c>
+      <c r="O80">
+        <v>-5.766340299199999</v>
+      </c>
+      <c r="P80">
+        <v>-22.2256029008</v>
+      </c>
+      <c r="Q80">
+        <v>-5.425602900800001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2392516388456853</v>
+      </c>
+      <c r="T80">
+        <v>3.389304937024545</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.1997390476483187</v>
+      </c>
+      <c r="W80">
+        <v>0.2864976845784185</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.9696070274190229</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2781035545172172</v>
+      </c>
+      <c r="C81">
+        <v>-33.54756308635888</v>
+      </c>
+      <c r="D81">
+        <v>22.08943691364112</v>
+      </c>
+      <c r="E81">
+        <v>10.477</v>
+      </c>
+      <c r="F81">
+        <v>60.277</v>
+      </c>
+      <c r="G81">
+        <v>4.64</v>
+      </c>
+      <c r="H81">
+        <v>26.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.02</v>
+      </c>
+      <c r="K81">
+        <v>16.8</v>
+      </c>
+      <c r="L81">
+        <v>-13.78</v>
+      </c>
+      <c r="M81">
+        <v>14.3941476</v>
+      </c>
+      <c r="N81">
+        <v>-28.1741476</v>
+      </c>
+      <c r="O81">
+        <v>-5.803874405599999</v>
+      </c>
+      <c r="P81">
+        <v>-22.3702731944</v>
+      </c>
+      <c r="Q81">
+        <v>-5.570273194400002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2487969549811941</v>
+      </c>
+      <c r="T81">
+        <v>3.55070041021619</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.1972107052730236</v>
+      </c>
+      <c r="W81">
+        <v>0.285893916419198</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.9573335207428331</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2801035545172172</v>
+      </c>
+      <c r="C82">
+        <v>-34.46001561216416</v>
+      </c>
+      <c r="D82">
+        <v>21.93998438783584</v>
+      </c>
+      <c r="E82">
+        <v>11.24</v>
+      </c>
+      <c r="F82">
+        <v>61.04</v>
+      </c>
+      <c r="G82">
+        <v>4.64</v>
+      </c>
+      <c r="H82">
+        <v>26.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.02</v>
+      </c>
+      <c r="K82">
+        <v>16.8</v>
+      </c>
+      <c r="L82">
+        <v>-13.78</v>
+      </c>
+      <c r="M82">
+        <v>14.576352</v>
+      </c>
+      <c r="N82">
+        <v>-28.356352</v>
+      </c>
+      <c r="O82">
+        <v>-5.841408511999999</v>
+      </c>
+      <c r="P82">
+        <v>-22.514943488</v>
+      </c>
+      <c r="Q82">
+        <v>-5.714943487999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2592968027302538</v>
+      </c>
+      <c r="T82">
+        <v>3.728235430726999</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.1947455714571108</v>
+      </c>
+      <c r="W82">
+        <v>0.2853052424639581</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.9453668517335476</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2821035545172172</v>
+      </c>
+      <c r="C83">
+        <v>-35.37045939940089</v>
+      </c>
+      <c r="D83">
+        <v>21.79254060059911</v>
+      </c>
+      <c r="E83">
+        <v>12.00300000000001</v>
+      </c>
+      <c r="F83">
+        <v>61.803</v>
+      </c>
+      <c r="G83">
+        <v>4.64</v>
+      </c>
+      <c r="H83">
+        <v>26.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.02</v>
+      </c>
+      <c r="K83">
+        <v>16.8</v>
+      </c>
+      <c r="L83">
+        <v>-13.78</v>
+      </c>
+      <c r="M83">
+        <v>14.7585564</v>
+      </c>
+      <c r="N83">
+        <v>-28.5385564</v>
+      </c>
+      <c r="O83">
+        <v>-5.8789426184</v>
+      </c>
+      <c r="P83">
+        <v>-22.6596137816</v>
+      </c>
+      <c r="Q83">
+        <v>-5.859613781600004</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2709018976107935</v>
+      </c>
+      <c r="T83">
+        <v>3.924458348133684</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.1923413051428254</v>
+      </c>
+      <c r="W83">
+        <v>0.2847311036681068</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.9336956560331335</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2841035545172172</v>
+      </c>
+      <c r="C84">
+        <v>-36.27893467584292</v>
+      </c>
+      <c r="D84">
+        <v>21.64706532415709</v>
+      </c>
+      <c r="E84">
+        <v>12.76600000000001</v>
+      </c>
+      <c r="F84">
+        <v>62.566</v>
+      </c>
+      <c r="G84">
+        <v>4.64</v>
+      </c>
+      <c r="H84">
+        <v>26.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.02</v>
+      </c>
+      <c r="K84">
+        <v>16.8</v>
+      </c>
+      <c r="L84">
+        <v>-13.78</v>
+      </c>
+      <c r="M84">
+        <v>14.9407608</v>
+      </c>
+      <c r="N84">
+        <v>-28.7207608</v>
+      </c>
+      <c r="O84">
+        <v>-5.916476724799999</v>
+      </c>
+      <c r="P84">
+        <v>-22.8042840752</v>
+      </c>
+      <c r="Q84">
+        <v>-6.004284075200001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2837964474780598</v>
+      </c>
+      <c r="T84">
+        <v>4.142483811918888</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.189995679470352</v>
+      </c>
+      <c r="W84">
+        <v>0.28417096825752</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.9223091236424854</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2861035545172172</v>
+      </c>
+      <c r="C85">
+        <v>-37.18548060223119</v>
+      </c>
+      <c r="D85">
+        <v>21.50351939776881</v>
+      </c>
+      <c r="E85">
+        <v>13.529</v>
+      </c>
+      <c r="F85">
+        <v>63.329</v>
+      </c>
+      <c r="G85">
+        <v>4.64</v>
+      </c>
+      <c r="H85">
+        <v>26.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.02</v>
+      </c>
+      <c r="K85">
+        <v>16.8</v>
+      </c>
+      <c r="L85">
+        <v>-13.78</v>
+      </c>
+      <c r="M85">
+        <v>15.1229652</v>
+      </c>
+      <c r="N85">
+        <v>-28.9029652</v>
+      </c>
+      <c r="O85">
+        <v>-5.9540108312</v>
+      </c>
+      <c r="P85">
+        <v>-22.9489543688</v>
+      </c>
+      <c r="Q85">
+        <v>-6.148954368800002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2982080032120633</v>
+      </c>
+      <c r="T85">
+        <v>4.386159330267058</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.18770657489842</v>
+      </c>
+      <c r="W85">
+        <v>0.2836243300857427</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.911196965526311</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2881035545172172</v>
+      </c>
+      <c r="C86">
+        <v>-38.09013530741912</v>
+      </c>
+      <c r="D86">
+        <v>21.36186469258088</v>
+      </c>
+      <c r="E86">
+        <v>14.292</v>
+      </c>
+      <c r="F86">
+        <v>64.092</v>
+      </c>
+      <c r="G86">
+        <v>4.64</v>
+      </c>
+      <c r="H86">
+        <v>26.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.02</v>
+      </c>
+      <c r="K86">
+        <v>16.8</v>
+      </c>
+      <c r="L86">
+        <v>-13.78</v>
+      </c>
+      <c r="M86">
+        <v>15.3051696</v>
+      </c>
+      <c r="N86">
+        <v>-29.0851696</v>
+      </c>
+      <c r="O86">
+        <v>-5.991544937599999</v>
+      </c>
+      <c r="P86">
+        <v>-23.0936246624</v>
+      </c>
+      <c r="Q86">
+        <v>-6.293624662400003</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3144210034128172</v>
+      </c>
+      <c r="T86">
+        <v>4.660294288408748</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.185471972816296</v>
+      </c>
+      <c r="W86">
+        <v>0.2830907071085315</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.9003493826033786</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2901035545172171</v>
+      </c>
+      <c r="C87">
+        <v>-38.99293592213806</v>
+      </c>
+      <c r="D87">
+        <v>21.22206407786193</v>
+      </c>
+      <c r="E87">
+        <v>15.05499999999999</v>
+      </c>
+      <c r="F87">
+        <v>64.85499999999999</v>
+      </c>
+      <c r="G87">
+        <v>4.64</v>
+      </c>
+      <c r="H87">
+        <v>26.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.02</v>
+      </c>
+      <c r="K87">
+        <v>16.8</v>
+      </c>
+      <c r="L87">
+        <v>-13.78</v>
+      </c>
+      <c r="M87">
+        <v>15.487374</v>
+      </c>
+      <c r="N87">
+        <v>-29.267374</v>
+      </c>
+      <c r="O87">
+        <v>-6.029079043999999</v>
+      </c>
+      <c r="P87">
+        <v>-23.238294956</v>
+      </c>
+      <c r="Q87">
+        <v>-6.438294956</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3327957369736717</v>
+      </c>
+      <c r="T87">
+        <v>4.970980574302664</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.1832899496066925</v>
+      </c>
+      <c r="W87">
+        <v>0.2825696399660781</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.889757036925692</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2921035545172173</v>
+      </c>
+      <c r="C88">
+        <v>-39.89391861144553</v>
+      </c>
+      <c r="D88">
+        <v>21.08408138855446</v>
+      </c>
+      <c r="E88">
+        <v>15.818</v>
+      </c>
+      <c r="F88">
+        <v>65.61799999999999</v>
+      </c>
+      <c r="G88">
+        <v>4.64</v>
+      </c>
+      <c r="H88">
+        <v>26.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.02</v>
+      </c>
+      <c r="K88">
+        <v>16.8</v>
+      </c>
+      <c r="L88">
+        <v>-13.78</v>
+      </c>
+      <c r="M88">
+        <v>15.6695784</v>
+      </c>
+      <c r="N88">
+        <v>-29.4495784</v>
+      </c>
+      <c r="O88">
+        <v>-6.066613150399998</v>
+      </c>
+      <c r="P88">
+        <v>-23.3829652496</v>
+      </c>
+      <c r="Q88">
+        <v>-6.582965249600001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3537954324717911</v>
+      </c>
+      <c r="T88">
+        <v>5.326050615324284</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.1811586711228938</v>
+      </c>
+      <c r="W88">
+        <v>0.2820606906641471</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.8794110248684166</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2941035545172172</v>
+      </c>
+      <c r="C89">
+        <v>-40.79311860591565</v>
+      </c>
+      <c r="D89">
+        <v>20.94788139408434</v>
+      </c>
+      <c r="E89">
+        <v>16.581</v>
+      </c>
+      <c r="F89">
+        <v>66.381</v>
+      </c>
+      <c r="G89">
+        <v>4.64</v>
+      </c>
+      <c r="H89">
+        <v>26.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.02</v>
+      </c>
+      <c r="K89">
+        <v>16.8</v>
+      </c>
+      <c r="L89">
+        <v>-13.78</v>
+      </c>
+      <c r="M89">
+        <v>15.8517828</v>
+      </c>
+      <c r="N89">
+        <v>-29.6317828</v>
+      </c>
+      <c r="O89">
+        <v>-6.104147256799999</v>
+      </c>
+      <c r="P89">
+        <v>-23.52763554320001</v>
+      </c>
+      <c r="Q89">
+        <v>-6.727635543200005</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3780258503542366</v>
+      </c>
+      <c r="T89">
+        <v>5.735746816503075</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.1790763875467685</v>
+      </c>
+      <c r="W89">
+        <v>0.2815634413461683</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.8693028521687796</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2961035545172172</v>
+      </c>
+      <c r="C90">
+        <v>-41.69057023162866</v>
+      </c>
+      <c r="D90">
+        <v>20.81342976837134</v>
+      </c>
+      <c r="E90">
+        <v>17.34399999999999</v>
+      </c>
+      <c r="F90">
+        <v>67.14399999999999</v>
+      </c>
+      <c r="G90">
+        <v>4.64</v>
+      </c>
+      <c r="H90">
+        <v>26.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.02</v>
+      </c>
+      <c r="K90">
+        <v>16.8</v>
+      </c>
+      <c r="L90">
+        <v>-13.78</v>
+      </c>
+      <c r="M90">
+        <v>16.0339872</v>
+      </c>
+      <c r="N90">
+        <v>-29.8139872</v>
+      </c>
+      <c r="O90">
+        <v>-6.141681363199999</v>
+      </c>
+      <c r="P90">
+        <v>-23.6723058368</v>
+      </c>
+      <c r="Q90">
+        <v>-6.872305836799999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4062946712170896</v>
+      </c>
+      <c r="T90">
+        <v>6.213725717878331</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.1770414285973735</v>
+      </c>
+      <c r="W90">
+        <v>0.2810774931490528</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.8594244106668616</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2981035545172173</v>
+      </c>
+      <c r="C91">
+        <v>-42.58630693901267</v>
+      </c>
+      <c r="D91">
+        <v>20.68069306098733</v>
+      </c>
+      <c r="E91">
+        <v>18.107</v>
+      </c>
+      <c r="F91">
+        <v>67.907</v>
+      </c>
+      <c r="G91">
+        <v>4.64</v>
+      </c>
+      <c r="H91">
+        <v>26.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.02</v>
+      </c>
+      <c r="K91">
+        <v>16.8</v>
+      </c>
+      <c r="L91">
+        <v>-13.78</v>
+      </c>
+      <c r="M91">
+        <v>16.2161916</v>
+      </c>
+      <c r="N91">
+        <v>-29.9961916</v>
+      </c>
+      <c r="O91">
+        <v>-6.179215469599999</v>
+      </c>
+      <c r="P91">
+        <v>-23.8169761304</v>
+      </c>
+      <c r="Q91">
+        <v>-7.0169761304</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4397032776913706</v>
+      </c>
+      <c r="T91">
+        <v>6.77860987404909</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.1750521990625715</v>
+      </c>
+      <c r="W91">
+        <v>0.2806024651361421</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.8497679566144249</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3001035545172172</v>
+      </c>
+      <c r="C92">
+        <v>-43.48036133058891</v>
+      </c>
+      <c r="D92">
+        <v>20.54963866941109</v>
+      </c>
+      <c r="E92">
+        <v>18.87</v>
+      </c>
+      <c r="F92">
+        <v>68.67</v>
+      </c>
+      <c r="G92">
+        <v>4.64</v>
+      </c>
+      <c r="H92">
+        <v>26.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.02</v>
+      </c>
+      <c r="K92">
+        <v>16.8</v>
+      </c>
+      <c r="L92">
+        <v>-13.78</v>
+      </c>
+      <c r="M92">
+        <v>16.398396</v>
+      </c>
+      <c r="N92">
+        <v>-30.178396</v>
+      </c>
+      <c r="O92">
+        <v>-6.216749576</v>
+      </c>
+      <c r="P92">
+        <v>-23.961646424</v>
+      </c>
+      <c r="Q92">
+        <v>-7.161646424000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4797936054605076</v>
+      </c>
+      <c r="T92">
+        <v>7.456470861453998</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.1731071746285429</v>
+      </c>
+      <c r="W92">
+        <v>0.2801379933012961</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.84032609042982</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3021035545172173</v>
+      </c>
+      <c r="C93">
+        <v>-44.37276518766865</v>
+      </c>
+      <c r="D93">
+        <v>20.42023481233135</v>
+      </c>
+      <c r="E93">
+        <v>19.633</v>
+      </c>
+      <c r="F93">
+        <v>69.43299999999999</v>
+      </c>
+      <c r="G93">
+        <v>4.64</v>
+      </c>
+      <c r="H93">
+        <v>26.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.02</v>
+      </c>
+      <c r="K93">
+        <v>16.8</v>
+      </c>
+      <c r="L93">
+        <v>-13.78</v>
+      </c>
+      <c r="M93">
+        <v>16.5806004</v>
+      </c>
+      <c r="N93">
+        <v>-30.3606004</v>
+      </c>
+      <c r="O93">
+        <v>-6.254283682399999</v>
+      </c>
+      <c r="P93">
+        <v>-24.1063167176</v>
+      </c>
+      <c r="Q93">
+        <v>-7.306316717600001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5287928949561197</v>
+      </c>
+      <c r="T93">
+        <v>8.284967623837778</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.1712048979842732</v>
+      </c>
+      <c r="W93">
+        <v>0.2796837296386445</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.8310917377877343</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3041035545172172</v>
+      </c>
+      <c r="C94">
+        <v>-45.26354949604774</v>
+      </c>
+      <c r="D94">
+        <v>20.29245050395226</v>
+      </c>
+      <c r="E94">
+        <v>20.396</v>
+      </c>
+      <c r="F94">
+        <v>70.196</v>
+      </c>
+      <c r="G94">
+        <v>4.64</v>
+      </c>
+      <c r="H94">
+        <v>26.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.02</v>
+      </c>
+      <c r="K94">
+        <v>16.8</v>
+      </c>
+      <c r="L94">
+        <v>-13.78</v>
+      </c>
+      <c r="M94">
+        <v>16.7628048</v>
+      </c>
+      <c r="N94">
+        <v>-30.5428048</v>
+      </c>
+      <c r="O94">
+        <v>-6.2918177888</v>
+      </c>
+      <c r="P94">
+        <v>-24.2509870112</v>
+      </c>
+      <c r="Q94">
+        <v>-7.450987011200002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5900420068256347</v>
+      </c>
+      <c r="T94">
+        <v>9.320588576817501</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.1693439751800963</v>
+      </c>
+      <c r="W94">
+        <v>0.279239341273007</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.8220581319422153</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3061035545172172</v>
+      </c>
+      <c r="C95">
+        <v>-46.15274447074248</v>
+      </c>
+      <c r="D95">
+        <v>20.16625552925753</v>
+      </c>
+      <c r="E95">
+        <v>21.15900000000001</v>
+      </c>
+      <c r="F95">
+        <v>70.959</v>
+      </c>
+      <c r="G95">
+        <v>4.64</v>
+      </c>
+      <c r="H95">
+        <v>26.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.02</v>
+      </c>
+      <c r="K95">
+        <v>16.8</v>
+      </c>
+      <c r="L95">
+        <v>-13.78</v>
+      </c>
+      <c r="M95">
+        <v>16.9450092</v>
+      </c>
+      <c r="N95">
+        <v>-30.7250092</v>
+      </c>
+      <c r="O95">
+        <v>-6.329351895199999</v>
+      </c>
+      <c r="P95">
+        <v>-24.3956573048</v>
+      </c>
+      <c r="Q95">
+        <v>-7.595657304800003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6687908649435825</v>
+      </c>
+      <c r="T95">
+        <v>10.65210123064857</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.1675230722211705</v>
+      </c>
+      <c r="W95">
+        <v>0.2788045096464155</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.8132187971901486</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3081035545172172</v>
+      </c>
+      <c r="C96">
+        <v>-47.04037957980803</v>
+      </c>
+      <c r="D96">
+        <v>20.04162042019198</v>
+      </c>
+      <c r="E96">
+        <v>21.92200000000001</v>
+      </c>
+      <c r="F96">
+        <v>71.72200000000001</v>
+      </c>
+      <c r="G96">
+        <v>4.64</v>
+      </c>
+      <c r="H96">
+        <v>26.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.02</v>
+      </c>
+      <c r="K96">
+        <v>16.8</v>
+      </c>
+      <c r="L96">
+        <v>-13.78</v>
+      </c>
+      <c r="M96">
+        <v>17.1272136</v>
+      </c>
+      <c r="N96">
+        <v>-30.90721360000001</v>
+      </c>
+      <c r="O96">
+        <v>-6.3668860016</v>
+      </c>
+      <c r="P96">
+        <v>-24.5403275984</v>
+      </c>
+      <c r="Q96">
+        <v>-7.740327598400004</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.77378934243418</v>
+      </c>
+      <c r="T96">
+        <v>12.42745143575667</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.1657409118783921</v>
+      </c>
+      <c r="W96">
+        <v>0.27837892975656</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.8045675333902531</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3101035545172173</v>
+      </c>
+      <c r="C97">
+        <v>-47.92648356727929</v>
+      </c>
+      <c r="D97">
+        <v>19.91851643272071</v>
+      </c>
+      <c r="E97">
+        <v>22.685</v>
+      </c>
+      <c r="F97">
+        <v>72.485</v>
+      </c>
+      <c r="G97">
+        <v>4.64</v>
+      </c>
+      <c r="H97">
+        <v>26.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.02</v>
+      </c>
+      <c r="K97">
+        <v>16.8</v>
+      </c>
+      <c r="L97">
+        <v>-13.78</v>
+      </c>
+      <c r="M97">
+        <v>17.309418</v>
+      </c>
+      <c r="N97">
+        <v>-31.089418</v>
+      </c>
+      <c r="O97">
+        <v>-6.404420107999999</v>
+      </c>
+      <c r="P97">
+        <v>-24.684997892</v>
+      </c>
+      <c r="Q97">
+        <v>-7.884997892000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9207872109210165</v>
+      </c>
+      <c r="T97">
+        <v>14.91294172290802</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.1639962707007249</v>
+      </c>
+      <c r="W97">
+        <v>0.2779623094433332</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.7960984014598296</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3121035545172173</v>
+      </c>
+      <c r="C98">
+        <v>-48.81108447527126</v>
+      </c>
+      <c r="D98">
+        <v>19.79691552472873</v>
+      </c>
+      <c r="E98">
+        <v>23.44799999999999</v>
+      </c>
+      <c r="F98">
+        <v>73.24799999999999</v>
+      </c>
+      <c r="G98">
+        <v>4.64</v>
+      </c>
+      <c r="H98">
+        <v>26.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.02</v>
+      </c>
+      <c r="K98">
+        <v>16.8</v>
+      </c>
+      <c r="L98">
+        <v>-13.78</v>
+      </c>
+      <c r="M98">
+        <v>17.4916224</v>
+      </c>
+      <c r="N98">
+        <v>-31.2716224</v>
+      </c>
+      <c r="O98">
+        <v>-6.441954214399998</v>
+      </c>
+      <c r="P98">
+        <v>-24.8296681856</v>
+      </c>
+      <c r="Q98">
+        <v>-8.029668185599999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.141284013651268</v>
+      </c>
+      <c r="T98">
+        <v>18.64117715363498</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.162287976214259</v>
+      </c>
+      <c r="W98">
+        <v>0.2775543687199651</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.7878057097779565</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3141035545172173</v>
+      </c>
+      <c r="C99">
+        <v>-49.69420966527486</v>
+      </c>
+      <c r="D99">
+        <v>19.67679033472513</v>
+      </c>
+      <c r="E99">
+        <v>24.211</v>
+      </c>
+      <c r="F99">
+        <v>74.011</v>
+      </c>
+      <c r="G99">
+        <v>4.64</v>
+      </c>
+      <c r="H99">
+        <v>26.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.02</v>
+      </c>
+      <c r="K99">
+        <v>16.8</v>
+      </c>
+      <c r="L99">
+        <v>-13.78</v>
+      </c>
+      <c r="M99">
+        <v>17.6738268</v>
+      </c>
+      <c r="N99">
+        <v>-31.4538268</v>
+      </c>
+      <c r="O99">
+        <v>-6.479488320799999</v>
+      </c>
+      <c r="P99">
+        <v>-24.9743384792</v>
+      </c>
+      <c r="Q99">
+        <v>-8.174338479200003</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.508778684868357</v>
+      </c>
+      <c r="T99">
+        <v>24.85490287151331</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.1606149042945244</v>
+      </c>
+      <c r="W99">
+        <v>0.2771548391455325</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.7796840014297299</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3161035545172172</v>
+      </c>
+      <c r="C100">
+        <v>-50.57588583868207</v>
+      </c>
+      <c r="D100">
+        <v>19.55811416131793</v>
+      </c>
+      <c r="E100">
+        <v>24.974</v>
+      </c>
+      <c r="F100">
+        <v>74.774</v>
+      </c>
+      <c r="G100">
+        <v>4.64</v>
+      </c>
+      <c r="H100">
+        <v>26.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.02</v>
+      </c>
+      <c r="K100">
+        <v>16.8</v>
+      </c>
+      <c r="L100">
+        <v>-13.78</v>
+      </c>
+      <c r="M100">
+        <v>17.8560312</v>
+      </c>
+      <c r="N100">
+        <v>-31.6360312</v>
+      </c>
+      <c r="O100">
+        <v>-6.517022427199999</v>
+      </c>
+      <c r="P100">
+        <v>-25.1190087728</v>
+      </c>
+      <c r="Q100">
+        <v>-8.3190087728</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.243768027302536</v>
+      </c>
+      <c r="T100">
+        <v>37.28235430726996</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.1589759766996823</v>
+      </c>
+      <c r="W100">
+        <v>0.2767634632358841</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.7717280422314674</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3181035545172172</v>
+      </c>
+      <c r="C101">
+        <v>-51.45613905657277</v>
+      </c>
+      <c r="D101">
+        <v>19.44086094342723</v>
+      </c>
+      <c r="E101">
+        <v>25.73699999999999</v>
+      </c>
+      <c r="F101">
+        <v>75.53699999999999</v>
+      </c>
+      <c r="G101">
+        <v>4.64</v>
+      </c>
+      <c r="H101">
+        <v>26.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.02</v>
+      </c>
+      <c r="K101">
+        <v>16.8</v>
+      </c>
+      <c r="L101">
+        <v>-13.78</v>
+      </c>
+      <c r="M101">
+        <v>18.0382356</v>
+      </c>
+      <c r="N101">
+        <v>-31.8182356</v>
+      </c>
+      <c r="O101">
+        <v>-6.554556533599999</v>
+      </c>
+      <c r="P101">
+        <v>-25.2636790664</v>
+      </c>
+      <c r="Q101">
+        <v>-8.463679066400001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.448736054605072</v>
+      </c>
+      <c r="T101">
+        <v>74.56470861453991</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.1573701587532208</v>
+      </c>
+      <c r="W101">
+        <v>0.2763799939102691</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.7639328094816547</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
